--- a/Spreadsheets/Fish_Export.xlsx
+++ b/Spreadsheets/Fish_Export.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pokemon TCG Legacy\Spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295BF4CC-A392-462A-AF05-FE3C247825AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E2B312-48B9-47B4-9D68-149CD1C2E5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fish" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="216">
   <si>
     <t>Location</t>
   </si>
@@ -1069,7 +1069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB78"/>
+  <dimension ref="A1:AC78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
@@ -1086,10 +1086,10 @@
     <col min="13" max="15" width="9" customWidth="1"/>
     <col min="16" max="16" width="8" customWidth="1"/>
     <col min="17" max="18" width="14" customWidth="1"/>
-    <col min="27" max="28" width="9.140625" style="11"/>
+    <col min="28" max="29" width="9.140625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1166,16 +1166,19 @@
         <v>212</v>
       </c>
       <c r="Z1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AB1" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="AB1" s="10" t="s">
+      <c r="AC1" s="10" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
@@ -1195,7 +1198,7 @@
         <v>45</v>
       </c>
       <c r="G2" s="4">
-        <f>F2/SUMIFS($F:$F,$A:$A,A2,$B:$B,B2)</f>
+        <f t="shared" ref="G2:G33" si="0">F2/SUMIFS($F:$F,$A:$A,A2,$B:$B,B2)</f>
         <v>0.45</v>
       </c>
       <c r="H2" s="3" t="b">
@@ -1235,27 +1238,27 @@
         <v>7.083333333333333</v>
       </c>
       <c r="S2">
-        <f>200/(F2/2)</f>
-        <v>8.8888888888888893</v>
+        <f>(200-F2*4)</f>
+        <v>20</v>
       </c>
       <c r="T2">
-        <f>IF(H2,200,50)</f>
-        <v>50</v>
+        <f>IF(H2,150,0)</f>
+        <v>0</v>
       </c>
       <c r="U2">
-        <f>100-(100*((1-I2)/2))*2</f>
+        <f>100*I2</f>
         <v>70</v>
       </c>
       <c r="V2">
-        <f>100+(100-L2)/2</f>
-        <v>90</v>
-      </c>
-      <c r="W2">
-        <f>(100/M2)</f>
-        <v>50</v>
-      </c>
-      <c r="X2">
-        <f>200/(N2*N2)*10</f>
+        <f>200/((L2/100)*(L2/100))</f>
+        <v>138.88888888888889</v>
+      </c>
+      <c r="W2" s="11">
+        <f>(200/M2)</f>
+        <v>100</v>
+      </c>
+      <c r="X2" s="11">
+        <f>(20/(N2*N2)*100)</f>
         <v>40.816326530612244</v>
       </c>
       <c r="Y2">
@@ -1263,19 +1266,23 @@
         <v>5</v>
       </c>
       <c r="Z2">
-        <f>P2/4</f>
-        <v>20</v>
-      </c>
-      <c r="AA2" s="11">
-        <f>SUM(S2:Z2)</f>
-        <v>334.70521541950114</v>
+        <f>K2/2</f>
+        <v>42.5</v>
+      </c>
+      <c r="AA2">
+        <f>P2/2</f>
+        <v>40</v>
       </c>
       <c r="AB2" s="11">
-        <f>AA2/10</f>
-        <v>33.470521541950113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+        <f>SUM(S2:AA2)</f>
+        <v>457.20521541950114</v>
+      </c>
+      <c r="AC2" s="11">
+        <f>AB2/10</f>
+        <v>45.720521541950113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -1295,7 +1302,7 @@
         <v>15</v>
       </c>
       <c r="G3" s="4">
-        <f>F3/SUMIFS($F:$F,$A:$A,A3,$B:$B,B3)</f>
+        <f t="shared" si="0"/>
         <v>0.15</v>
       </c>
       <c r="H3" s="3" t="b">
@@ -1335,47 +1342,51 @@
         <v>11.666666666666666</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S66" si="0">200/(F3/2)</f>
-        <v>26.666666666666668</v>
+        <f t="shared" ref="S3:S66" si="1">(200-F3*4)</f>
+        <v>140</v>
       </c>
       <c r="T3">
-        <f t="shared" ref="T3:T66" si="1">IF(H3,200,50)</f>
-        <v>200</v>
+        <f t="shared" ref="T3:T66" si="2">IF(H3,150,0)</f>
+        <v>150</v>
       </c>
       <c r="U3">
-        <f t="shared" ref="U3:U66" si="2">100-(100*((1-I3)/2))*2</f>
+        <f t="shared" ref="U3:U66" si="3">100*I3</f>
         <v>60</v>
       </c>
       <c r="V3">
-        <f t="shared" ref="V3:V66" si="3">100+(100-L3)/2</f>
-        <v>107.5</v>
-      </c>
-      <c r="W3">
-        <f t="shared" ref="W3:W66" si="4">(100/M3)</f>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X3">
-        <f t="shared" ref="X3:X66" si="5">200/(N3*N3)*10</f>
+        <f t="shared" ref="V3:V66" si="4">200/((L3/100)*(L3/100))</f>
+        <v>276.8166089965398</v>
+      </c>
+      <c r="W3" s="11">
+        <f t="shared" ref="W3:W66" si="5">(200/M3)</f>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X3" s="11">
+        <f t="shared" ref="X3:X66" si="6">(20/(N3*N3)*100)</f>
         <v>80</v>
       </c>
       <c r="Y3">
-        <f t="shared" ref="Y3:Y66" si="6">O3/2</f>
+        <f t="shared" ref="Y3:Y66" si="7">O3/2</f>
         <v>60</v>
       </c>
       <c r="Z3">
-        <f t="shared" ref="Z3:Z66" si="7">P3/2</f>
+        <f t="shared" ref="Z3:Z66" si="8">K3/2</f>
+        <v>70</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" ref="AA3:AA66" si="9">P3/2</f>
         <v>55</v>
       </c>
-      <c r="AA3" s="11">
-        <f t="shared" ref="AA3:AA66" si="8">SUM(S3:Z3)</f>
-        <v>655.83333333333326</v>
-      </c>
       <c r="AB3" s="11">
-        <f t="shared" ref="AB3:AB66" si="9">AA3/10</f>
-        <v>65.583333333333329</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" ref="AB3:AB66" si="10">SUM(S3:AA3)</f>
+        <v>1025.1499423298733</v>
+      </c>
+      <c r="AC3" s="11">
+        <f t="shared" ref="AC3:AC66" si="11">AB3/10</f>
+        <v>102.51499423298733</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
@@ -1395,7 +1406,7 @@
         <v>35</v>
       </c>
       <c r="G4" s="4">
-        <f>F4/SUMIFS($F:$F,$A:$A,A4,$B:$B,B4)</f>
+        <f t="shared" si="0"/>
         <v>0.35</v>
       </c>
       <c r="H4" s="3" t="b">
@@ -1435,47 +1446,51 @@
         <v>6.666666666666667</v>
       </c>
       <c r="S4">
-        <f t="shared" si="0"/>
-        <v>11.428571428571429</v>
+        <f t="shared" si="1"/>
+        <v>60</v>
       </c>
       <c r="T4">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="V4">
-        <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="W4">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X4">
+        <v>246.91358024691357</v>
+      </c>
+      <c r="W4" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X4" s="11">
+        <f t="shared" si="6"/>
         <v>40.816326530612244</v>
       </c>
       <c r="Y4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>40</v>
+      </c>
+      <c r="AA4">
+        <f t="shared" si="9"/>
         <v>45</v>
       </c>
-      <c r="AA4" s="11">
-        <f t="shared" si="8"/>
-        <v>388.91156462585036</v>
-      </c>
       <c r="AB4" s="11">
-        <f t="shared" si="9"/>
-        <v>38.891156462585037</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>636.06324011085917</v>
+      </c>
+      <c r="AC4" s="11">
+        <f t="shared" si="11"/>
+        <v>63.606324011085917</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
@@ -1495,7 +1510,7 @@
         <v>5</v>
       </c>
       <c r="G5" s="4">
-        <f>F5/SUMIFS($F:$F,$A:$A,A5,$B:$B,B5)</f>
+        <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
       <c r="H5" s="3" t="b">
@@ -1535,47 +1550,51 @@
         <v>10</v>
       </c>
       <c r="S5">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <f t="shared" si="1"/>
+        <v>180</v>
       </c>
       <c r="T5">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="V5">
-        <f t="shared" si="3"/>
-        <v>110</v>
-      </c>
-      <c r="W5">
         <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="X5">
+        <v>312.49999999999994</v>
+      </c>
+      <c r="W5" s="11">
         <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
+      <c r="X5" s="11">
+        <f t="shared" si="6"/>
         <v>40.816326530612244</v>
       </c>
       <c r="Y5">
-        <f t="shared" si="6"/>
-        <v>55</v>
-      </c>
-      <c r="Z5">
         <f t="shared" si="7"/>
         <v>55</v>
       </c>
-      <c r="AA5" s="11">
+      <c r="Z5">
         <f t="shared" si="8"/>
-        <v>660.81632653061229</v>
+        <v>60</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" si="9"/>
+        <v>55</v>
       </c>
       <c r="AB5" s="11">
-        <f t="shared" si="9"/>
-        <v>66.081632653061234</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1013.3163265306123</v>
+      </c>
+      <c r="AC5" s="11">
+        <f t="shared" si="11"/>
+        <v>101.33163265306123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -1595,7 +1614,7 @@
         <v>45</v>
       </c>
       <c r="G6" s="4">
-        <f>F6/SUMIFS($F:$F,$A:$A,A6,$B:$B,B6)</f>
+        <f t="shared" si="0"/>
         <v>0.45</v>
       </c>
       <c r="H6" s="3" t="b">
@@ -1635,47 +1654,51 @@
         <v>6.666666666666667</v>
       </c>
       <c r="S6">
-        <f t="shared" si="0"/>
-        <v>8.8888888888888893</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="T6">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="V6">
-        <f t="shared" si="3"/>
-        <v>75</v>
-      </c>
-      <c r="W6">
         <f t="shared" si="4"/>
+        <v>88.888888888888886</v>
+      </c>
+      <c r="W6" s="11">
+        <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
+      <c r="X6" s="11">
+        <f t="shared" si="6"/>
+        <v>40.816326530612244</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
-      <c r="X6">
-        <f t="shared" si="5"/>
-        <v>40.816326530612244</v>
-      </c>
-      <c r="Y6">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="Z6">
-        <f t="shared" si="7"/>
+      <c r="AA6">
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
-      <c r="AA6" s="11">
-        <f t="shared" si="8"/>
-        <v>339.70521541950114</v>
-      </c>
       <c r="AB6" s="11">
-        <f t="shared" si="9"/>
-        <v>33.970521541950113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>394.70521541950114</v>
+      </c>
+      <c r="AC6" s="11">
+        <f t="shared" si="11"/>
+        <v>39.470521541950113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
@@ -1695,7 +1718,7 @@
         <v>15</v>
       </c>
       <c r="G7" s="4">
-        <f>F7/SUMIFS($F:$F,$A:$A,A7,$B:$B,B7)</f>
+        <f t="shared" si="0"/>
         <v>0.15</v>
       </c>
       <c r="H7" s="3" t="b">
@@ -1735,47 +1758,51 @@
         <v>9.1666666666666661</v>
       </c>
       <c r="S7">
-        <f t="shared" si="0"/>
-        <v>26.666666666666668</v>
+        <f t="shared" si="1"/>
+        <v>140</v>
       </c>
       <c r="T7">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="V7">
-        <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="W7">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X7">
+        <v>246.91358024691357</v>
+      </c>
+      <c r="W7" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X7" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="Z7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>55</v>
       </c>
-      <c r="AA7" s="11">
-        <f t="shared" si="8"/>
-        <v>653.33333333333326</v>
+      <c r="AA7">
+        <f t="shared" si="9"/>
+        <v>55</v>
       </c>
       <c r="AB7" s="11">
-        <f t="shared" si="9"/>
-        <v>65.333333333333329</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>980.246913580247</v>
+      </c>
+      <c r="AC7" s="11">
+        <f t="shared" si="11"/>
+        <v>98.024691358024697</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
@@ -1795,7 +1822,7 @@
         <v>35</v>
       </c>
       <c r="G8" s="4">
-        <f>F8/SUMIFS($F:$F,$A:$A,A8,$B:$B,B8)</f>
+        <f t="shared" si="0"/>
         <v>0.35</v>
       </c>
       <c r="H8" s="3" t="b">
@@ -1835,47 +1862,51 @@
         <v>7.5</v>
       </c>
       <c r="S8">
-        <f t="shared" si="0"/>
-        <v>11.428571428571429</v>
+        <f t="shared" si="1"/>
+        <v>60</v>
       </c>
       <c r="T8">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="V8">
-        <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="W8">
         <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="X8">
+        <v>165.28925619834709</v>
+      </c>
+      <c r="W8" s="11">
         <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="X8" s="11">
+        <f t="shared" si="6"/>
         <v>40.816326530612244</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.5</v>
       </c>
       <c r="Z8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>45</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="9"/>
         <v>35</v>
       </c>
-      <c r="AA8" s="11">
-        <f t="shared" si="8"/>
-        <v>359.74489795918367</v>
-      </c>
       <c r="AB8" s="11">
-        <f t="shared" si="9"/>
-        <v>35.974489795918366</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>523.60558272895923</v>
+      </c>
+      <c r="AC8" s="11">
+        <f t="shared" si="11"/>
+        <v>52.360558272895922</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -1895,7 +1926,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="4">
-        <f>F9/SUMIFS($F:$F,$A:$A,A9,$B:$B,B9)</f>
+        <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
       <c r="H9" s="3" t="b">
@@ -1935,47 +1966,51 @@
         <v>12.5</v>
       </c>
       <c r="S9">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <f t="shared" si="1"/>
+        <v>180</v>
       </c>
       <c r="T9">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="V9">
-        <f t="shared" si="3"/>
-        <v>110</v>
-      </c>
-      <c r="W9">
         <f t="shared" si="4"/>
+        <v>312.49999999999994</v>
+      </c>
+      <c r="W9" s="11">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="X9" s="11">
+        <f t="shared" si="6"/>
+        <v>80</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="7"/>
+        <v>65</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="8"/>
+        <v>75</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" si="9"/>
         <v>50</v>
       </c>
-      <c r="X9">
-        <f t="shared" si="5"/>
-        <v>80</v>
-      </c>
-      <c r="Y9">
-        <f t="shared" si="6"/>
-        <v>65</v>
-      </c>
-      <c r="Z9">
-        <f t="shared" si="7"/>
-        <v>50</v>
-      </c>
-      <c r="AA9" s="11">
-        <f t="shared" si="8"/>
-        <v>705</v>
-      </c>
       <c r="AB9" s="11">
-        <f t="shared" si="9"/>
-        <v>70.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1082.5</v>
+      </c>
+      <c r="AC9" s="11">
+        <f t="shared" si="11"/>
+        <v>108.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -1995,7 +2030,7 @@
         <v>30</v>
       </c>
       <c r="G10" s="4">
-        <f>F10/SUMIFS($F:$F,$A:$A,A10,$B:$B,B10)</f>
+        <f t="shared" si="0"/>
         <v>0.3</v>
       </c>
       <c r="H10" s="3" t="b">
@@ -2035,47 +2070,51 @@
         <v>7.5</v>
       </c>
       <c r="S10">
-        <f t="shared" si="0"/>
-        <v>13.333333333333334</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
       <c r="T10">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="V10">
-        <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="W10">
         <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="X10">
+        <v>165.28925619834709</v>
+      </c>
+      <c r="W10" s="11">
         <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="X10" s="11">
+        <f t="shared" si="6"/>
         <v>40.816326530612244</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>37.5</v>
       </c>
       <c r="Z10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>45</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
-      <c r="AA10" s="11">
-        <f t="shared" si="8"/>
-        <v>376.6496598639456</v>
-      </c>
       <c r="AB10" s="11">
-        <f t="shared" si="9"/>
-        <v>37.664965986394563</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>558.60558272895923</v>
+      </c>
+      <c r="AC10" s="11">
+        <f t="shared" si="11"/>
+        <v>55.860558272895922</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -2095,7 +2134,7 @@
         <v>45</v>
       </c>
       <c r="G11" s="4">
-        <f>F11/SUMIFS($F:$F,$A:$A,A11,$B:$B,B11)</f>
+        <f t="shared" si="0"/>
         <v>0.45</v>
       </c>
       <c r="H11" s="3" t="b">
@@ -2135,47 +2174,51 @@
         <v>7.5</v>
       </c>
       <c r="S11">
-        <f t="shared" si="0"/>
-        <v>8.8888888888888893</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="T11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="4"/>
+        <v>138.88888888888889</v>
+      </c>
+      <c r="W11" s="11">
+        <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
+      <c r="X11" s="11">
+        <f t="shared" si="6"/>
+        <v>40.816326530612244</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="8"/>
+        <v>45</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="9"/>
         <v>50</v>
       </c>
-      <c r="U11">
-        <f t="shared" si="2"/>
-        <v>80</v>
-      </c>
-      <c r="V11">
-        <f t="shared" si="3"/>
-        <v>90</v>
-      </c>
-      <c r="W11">
-        <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="X11">
-        <f t="shared" si="5"/>
-        <v>40.816326530612244</v>
-      </c>
-      <c r="Y11">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="Z11">
-        <f t="shared" si="7"/>
-        <v>50</v>
-      </c>
-      <c r="AA11" s="11">
-        <f t="shared" si="8"/>
-        <v>364.70521541950114</v>
-      </c>
       <c r="AB11" s="11">
-        <f t="shared" si="9"/>
-        <v>36.470521541950113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>459.70521541950114</v>
+      </c>
+      <c r="AC11" s="11">
+        <f t="shared" si="11"/>
+        <v>45.970521541950113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -2195,7 +2238,7 @@
         <v>20</v>
       </c>
       <c r="G12" s="4">
-        <f>F12/SUMIFS($F:$F,$A:$A,A12,$B:$B,B12)</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="H12" s="3" t="b">
@@ -2235,47 +2278,51 @@
         <v>10</v>
       </c>
       <c r="S12">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>120</v>
       </c>
       <c r="T12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="3"/>
+        <v>70</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="4"/>
         <v>200</v>
       </c>
-      <c r="U12">
-        <f t="shared" si="2"/>
-        <v>70</v>
-      </c>
-      <c r="V12">
-        <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-      <c r="W12">
-        <f t="shared" si="4"/>
+      <c r="W12" s="11">
+        <f t="shared" si="5"/>
+        <v>111.11111111111111</v>
+      </c>
+      <c r="X12" s="11">
+        <f t="shared" si="6"/>
         <v>55.555555555555557</v>
       </c>
-      <c r="X12">
-        <f t="shared" si="5"/>
-        <v>55.555555555555557</v>
-      </c>
       <c r="Y12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="Z12">
-        <f t="shared" si="7"/>
-        <v>80</v>
-      </c>
-      <c r="AA12" s="11">
         <f t="shared" si="8"/>
-        <v>631.11111111111109</v>
+        <v>60</v>
+      </c>
+      <c r="AA12">
+        <f t="shared" si="9"/>
+        <v>80</v>
       </c>
       <c r="AB12" s="11">
-        <f t="shared" si="9"/>
-        <v>63.111111111111107</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>896.66666666666663</v>
+      </c>
+      <c r="AC12" s="11">
+        <f t="shared" si="11"/>
+        <v>89.666666666666657</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
@@ -2295,7 +2342,7 @@
         <v>5</v>
       </c>
       <c r="G13" s="4">
-        <f>F13/SUMIFS($F:$F,$A:$A,A13,$B:$B,B13)</f>
+        <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
       <c r="H13" s="3" t="b">
@@ -2335,47 +2382,51 @@
         <v>12.5</v>
       </c>
       <c r="S13">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <f t="shared" si="1"/>
+        <v>180</v>
       </c>
       <c r="T13">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="V13">
-        <f t="shared" si="3"/>
-        <v>110</v>
-      </c>
-      <c r="W13">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X13">
+        <v>312.49999999999994</v>
+      </c>
+      <c r="W13" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X13" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>75</v>
       </c>
       <c r="Z13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>75</v>
+      </c>
+      <c r="AA13">
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AA13" s="11">
-        <f t="shared" si="8"/>
-        <v>791.66666666666663</v>
-      </c>
       <c r="AB13" s="11">
-        <f t="shared" si="9"/>
-        <v>79.166666666666657</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1185.8333333333335</v>
+      </c>
+      <c r="AC13" s="11">
+        <f t="shared" si="11"/>
+        <v>118.58333333333334</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
@@ -2395,7 +2446,7 @@
         <v>42</v>
       </c>
       <c r="G14" s="4">
-        <f>F14/SUMIFS($F:$F,$A:$A,A14,$B:$B,B14)</f>
+        <f t="shared" si="0"/>
         <v>0.42</v>
       </c>
       <c r="H14" s="3" t="b">
@@ -2435,47 +2486,51 @@
         <v>6.666666666666667</v>
       </c>
       <c r="S14">
-        <f t="shared" si="0"/>
-        <v>9.5238095238095237</v>
+        <f t="shared" si="1"/>
+        <v>32</v>
       </c>
       <c r="T14">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="V14">
-        <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="W14">
         <f t="shared" si="4"/>
+        <v>102.04081632653063</v>
+      </c>
+      <c r="W14" s="11">
+        <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
+      <c r="X14" s="11">
+        <f t="shared" si="6"/>
+        <v>40.816326530612244</v>
+      </c>
+      <c r="Y14">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="Z14">
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
-      <c r="X14">
-        <f t="shared" si="5"/>
-        <v>40.816326530612244</v>
-      </c>
-      <c r="Y14">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="Z14">
-        <f t="shared" si="7"/>
+      <c r="AA14">
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
-      <c r="AA14" s="11">
-        <f t="shared" si="8"/>
-        <v>325.34013605442175</v>
-      </c>
       <c r="AB14" s="11">
-        <f t="shared" si="9"/>
-        <v>32.534013605442176</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>399.85714285714283</v>
+      </c>
+      <c r="AC14" s="11">
+        <f t="shared" si="11"/>
+        <v>39.98571428571428</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
@@ -2495,7 +2550,7 @@
         <v>15</v>
       </c>
       <c r="G15" s="4">
-        <f>F15/SUMIFS($F:$F,$A:$A,A15,$B:$B,B15)</f>
+        <f t="shared" si="0"/>
         <v>0.15</v>
       </c>
       <c r="H15" s="3" t="b">
@@ -2535,47 +2590,51 @@
         <v>10</v>
       </c>
       <c r="S15">
-        <f t="shared" si="0"/>
-        <v>26.666666666666668</v>
+        <f t="shared" si="1"/>
+        <v>140</v>
       </c>
       <c r="T15">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="V15">
-        <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="W15">
         <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="X15">
+        <v>246.91358024691357</v>
+      </c>
+      <c r="W15" s="11">
         <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="X15" s="11">
+        <f t="shared" si="6"/>
         <v>55.555555555555557</v>
       </c>
       <c r="Y15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
       <c r="Z15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>60</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
-      <c r="AA15" s="11">
-        <f t="shared" si="8"/>
-        <v>562.22222222222217</v>
-      </c>
       <c r="AB15" s="11">
-        <f t="shared" si="9"/>
-        <v>56.222222222222214</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>877.46913580246917</v>
+      </c>
+      <c r="AC15" s="11">
+        <f t="shared" si="11"/>
+        <v>87.746913580246911</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
@@ -2595,7 +2654,7 @@
         <v>33</v>
       </c>
       <c r="G16" s="4">
-        <f>F16/SUMIFS($F:$F,$A:$A,A16,$B:$B,B16)</f>
+        <f t="shared" si="0"/>
         <v>0.33</v>
       </c>
       <c r="H16" s="3" t="b">
@@ -2635,47 +2694,51 @@
         <v>6.25</v>
       </c>
       <c r="S16">
-        <f t="shared" si="0"/>
-        <v>12.121212121212121</v>
+        <f t="shared" si="1"/>
+        <v>68</v>
       </c>
       <c r="T16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="U16">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
       <c r="V16">
-        <f t="shared" si="3"/>
-        <v>75</v>
-      </c>
-      <c r="W16">
         <f t="shared" si="4"/>
-        <v>33.333333333333336</v>
-      </c>
-      <c r="X16">
+        <v>88.888888888888886</v>
+      </c>
+      <c r="W16" s="11">
         <f t="shared" si="5"/>
+        <v>66.666666666666671</v>
+      </c>
+      <c r="X16" s="11">
+        <f t="shared" si="6"/>
         <v>40.816326530612244</v>
       </c>
       <c r="Y16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="Z16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>37.5</v>
+      </c>
+      <c r="AA16">
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
-      <c r="AA16" s="11">
-        <f t="shared" si="8"/>
-        <v>296.27087198515773</v>
-      </c>
       <c r="AB16" s="11">
-        <f t="shared" si="9"/>
-        <v>29.627087198515774</v>
-      </c>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>386.87188208616777</v>
+      </c>
+      <c r="AC16" s="11">
+        <f t="shared" si="11"/>
+        <v>38.687188208616774</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
@@ -2695,7 +2758,7 @@
         <v>10</v>
       </c>
       <c r="G17" s="4">
-        <f>F17/SUMIFS($F:$F,$A:$A,A17,$B:$B,B17)</f>
+        <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
       <c r="H17" s="3" t="b">
@@ -2735,47 +2798,51 @@
         <v>10</v>
       </c>
       <c r="S17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="V17">
+        <f t="shared" si="4"/>
+        <v>246.91358024691357</v>
+      </c>
+      <c r="W17" s="11">
+        <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
+      <c r="X17" s="11">
+        <f t="shared" si="6"/>
+        <v>80</v>
+      </c>
+      <c r="Y17">
+        <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+      <c r="Z17">
+        <f t="shared" si="8"/>
+        <v>60</v>
+      </c>
+      <c r="AA17">
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
-      <c r="T17">
-        <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="U17">
-        <f t="shared" si="2"/>
-        <v>80</v>
-      </c>
-      <c r="V17">
-        <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="W17">
-        <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="X17">
-        <f t="shared" si="5"/>
-        <v>80</v>
-      </c>
-      <c r="Y17">
-        <f t="shared" si="6"/>
-        <v>25</v>
-      </c>
-      <c r="Z17">
-        <f t="shared" si="7"/>
-        <v>40</v>
-      </c>
-      <c r="AA17" s="11">
-        <f t="shared" si="8"/>
-        <v>610</v>
-      </c>
       <c r="AB17" s="11">
-        <f t="shared" si="9"/>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>921.91358024691363</v>
+      </c>
+      <c r="AC17" s="11">
+        <f t="shared" si="11"/>
+        <v>92.191358024691368</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>55</v>
       </c>
@@ -2795,7 +2862,7 @@
         <v>35</v>
       </c>
       <c r="G18" s="4">
-        <f>F18/SUMIFS($F:$F,$A:$A,A18,$B:$B,B18)</f>
+        <f t="shared" si="0"/>
         <v>0.35</v>
       </c>
       <c r="H18" s="3" t="b">
@@ -2835,47 +2902,51 @@
         <v>7.083333333333333</v>
       </c>
       <c r="S18">
-        <f t="shared" si="0"/>
-        <v>11.428571428571429</v>
+        <f t="shared" si="1"/>
+        <v>60</v>
       </c>
       <c r="T18">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="V18">
-        <f t="shared" si="3"/>
-        <v>92.5</v>
-      </c>
-      <c r="W18">
         <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="X18">
+        <v>151.2287334593573</v>
+      </c>
+      <c r="W18" s="11">
         <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="X18" s="11">
+        <f t="shared" si="6"/>
         <v>40.816326530612244</v>
       </c>
       <c r="Y18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="Z18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>42.5</v>
+      </c>
+      <c r="AA18">
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
-      <c r="AA18" s="11">
-        <f t="shared" si="8"/>
-        <v>359.74489795918367</v>
-      </c>
       <c r="AB18" s="11">
-        <f t="shared" si="9"/>
-        <v>35.974489795918366</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>509.5450599899695</v>
+      </c>
+      <c r="AC18" s="11">
+        <f t="shared" si="11"/>
+        <v>50.95450599899695</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>55</v>
       </c>
@@ -2895,7 +2966,7 @@
         <v>5</v>
       </c>
       <c r="G19" s="4">
-        <f>F19/SUMIFS($F:$F,$A:$A,A19,$B:$B,B19)</f>
+        <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
       <c r="H19" s="3" t="b">
@@ -2935,47 +3006,51 @@
         <v>11.666666666666666</v>
       </c>
       <c r="S19">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <f t="shared" si="1"/>
+        <v>180</v>
       </c>
       <c r="T19">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="V19">
-        <f t="shared" si="3"/>
-        <v>110</v>
-      </c>
-      <c r="W19">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X19">
+        <v>312.49999999999994</v>
+      </c>
+      <c r="W19" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X19" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>35</v>
       </c>
       <c r="Z19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>70</v>
+      </c>
+      <c r="AA19">
+        <f t="shared" si="9"/>
         <v>60</v>
       </c>
-      <c r="AA19" s="11">
-        <f t="shared" si="8"/>
-        <v>691.66666666666663</v>
-      </c>
       <c r="AB19" s="11">
-        <f t="shared" si="9"/>
-        <v>69.166666666666657</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1080.8333333333335</v>
+      </c>
+      <c r="AC19" s="11">
+        <f t="shared" si="11"/>
+        <v>108.08333333333334</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>55</v>
       </c>
@@ -2995,7 +3070,7 @@
         <v>33</v>
       </c>
       <c r="G20" s="4">
-        <f>F20/SUMIFS($F:$F,$A:$A,A20,$B:$B,B20)</f>
+        <f t="shared" si="0"/>
         <v>0.33</v>
       </c>
       <c r="H20" s="3" t="b">
@@ -3035,47 +3110,51 @@
         <v>4.166666666666667</v>
       </c>
       <c r="S20">
-        <f t="shared" si="0"/>
-        <v>12.121212121212121</v>
+        <f t="shared" si="1"/>
+        <v>68</v>
       </c>
       <c r="T20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="U20">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
       <c r="V20">
-        <f t="shared" si="3"/>
-        <v>75</v>
-      </c>
-      <c r="W20">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X20">
+        <v>88.888888888888886</v>
+      </c>
+      <c r="W20" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X20" s="11">
+        <f t="shared" si="6"/>
         <v>35.555555555555557</v>
       </c>
       <c r="Y20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>25</v>
+      </c>
+      <c r="AA20">
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="AA20" s="11">
-        <f t="shared" si="8"/>
-        <v>309.34343434343435</v>
-      </c>
       <c r="AB20" s="11">
-        <f t="shared" si="9"/>
-        <v>30.934343434343436</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>420.77777777777777</v>
+      </c>
+      <c r="AC20" s="11">
+        <f t="shared" si="11"/>
+        <v>42.077777777777776</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>55</v>
       </c>
@@ -3095,7 +3174,7 @@
         <v>22</v>
       </c>
       <c r="G21" s="4">
-        <f>F21/SUMIFS($F:$F,$A:$A,A21,$B:$B,B21)</f>
+        <f t="shared" si="0"/>
         <v>0.22</v>
       </c>
       <c r="H21" s="3" t="b">
@@ -3135,47 +3214,51 @@
         <v>6.25</v>
       </c>
       <c r="S21">
-        <f t="shared" si="0"/>
-        <v>18.181818181818183</v>
+        <f t="shared" si="1"/>
+        <v>112</v>
       </c>
       <c r="T21">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="V21">
-        <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="W21">
         <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="X21">
+        <v>165.28925619834709</v>
+      </c>
+      <c r="W21" s="11">
         <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="X21" s="11">
+        <f t="shared" si="6"/>
         <v>35.555555555555557</v>
       </c>
       <c r="Y21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>37.5</v>
+      </c>
+      <c r="AA21">
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
-      <c r="AA21" s="11">
-        <f t="shared" si="8"/>
-        <v>338.73737373737373</v>
-      </c>
       <c r="AB21" s="11">
-        <f t="shared" si="9"/>
-        <v>33.87373737373737</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>540.3448117539026</v>
+      </c>
+      <c r="AC21" s="11">
+        <f t="shared" si="11"/>
+        <v>54.034481175390262</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>55</v>
       </c>
@@ -3195,7 +3278,7 @@
         <v>5</v>
       </c>
       <c r="G22" s="4">
-        <f>F22/SUMIFS($F:$F,$A:$A,A22,$B:$B,B22)</f>
+        <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
       <c r="H22" s="3" t="b">
@@ -3235,47 +3318,51 @@
         <v>13.333333333333334</v>
       </c>
       <c r="S22">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <f t="shared" si="1"/>
+        <v>180</v>
       </c>
       <c r="T22">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="V22">
-        <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="W22">
         <f t="shared" si="4"/>
-        <v>33.333333333333336</v>
-      </c>
-      <c r="X22">
+        <v>246.91358024691357</v>
+      </c>
+      <c r="W22" s="11">
         <f t="shared" si="5"/>
+        <v>66.666666666666671</v>
+      </c>
+      <c r="X22" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
       <c r="Z22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>80</v>
+      </c>
+      <c r="AA22">
+        <f t="shared" si="9"/>
         <v>45</v>
       </c>
-      <c r="AA22" s="11">
-        <f t="shared" si="8"/>
-        <v>598.33333333333326</v>
-      </c>
       <c r="AB22" s="11">
-        <f t="shared" si="9"/>
-        <v>59.833333333333329</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>903.58024691358025</v>
+      </c>
+      <c r="AC22" s="11">
+        <f t="shared" si="11"/>
+        <v>90.358024691358025</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>55</v>
       </c>
@@ -3295,7 +3382,7 @@
         <v>29</v>
       </c>
       <c r="G23" s="4">
-        <f>F23/SUMIFS($F:$F,$A:$A,A23,$B:$B,B23)</f>
+        <f t="shared" si="0"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="H23" s="3" t="b">
@@ -3335,47 +3422,51 @@
         <v>7.5</v>
       </c>
       <c r="S23">
-        <f t="shared" si="0"/>
-        <v>13.793103448275861</v>
+        <f t="shared" si="1"/>
+        <v>84</v>
       </c>
       <c r="T23">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="V23">
-        <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="W23">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X23">
+        <v>246.91358024691357</v>
+      </c>
+      <c r="W23" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X23" s="11">
+        <f t="shared" si="6"/>
         <v>55.555555555555557</v>
       </c>
       <c r="Y23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12.5</v>
       </c>
       <c r="Z23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>45</v>
+      </c>
+      <c r="AA23">
+        <f t="shared" si="9"/>
         <v>65</v>
       </c>
-      <c r="AA23" s="11">
-        <f t="shared" si="8"/>
-        <v>458.5153256704981</v>
-      </c>
       <c r="AB23" s="11">
-        <f t="shared" si="9"/>
-        <v>45.851532567049809</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>732.30246913580243</v>
+      </c>
+      <c r="AC23" s="11">
+        <f t="shared" si="11"/>
+        <v>73.230246913580245</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>55</v>
       </c>
@@ -3395,7 +3486,7 @@
         <v>30</v>
       </c>
       <c r="G24" s="4">
-        <f>F24/SUMIFS($F:$F,$A:$A,A24,$B:$B,B24)</f>
+        <f t="shared" si="0"/>
         <v>0.3</v>
       </c>
       <c r="H24" s="3" t="b">
@@ -3435,47 +3526,51 @@
         <v>7.5</v>
       </c>
       <c r="S24">
-        <f t="shared" si="0"/>
-        <v>13.333333333333334</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
       <c r="T24">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="V24">
-        <f t="shared" si="3"/>
-        <v>90</v>
-      </c>
-      <c r="W24">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X24">
+        <v>138.88888888888889</v>
+      </c>
+      <c r="W24" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X24" s="11">
+        <f t="shared" si="6"/>
         <v>40.816326530612244</v>
       </c>
       <c r="Y24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12.5</v>
       </c>
       <c r="Z24">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>45</v>
+      </c>
+      <c r="AA24">
+        <f t="shared" si="9"/>
         <v>70</v>
       </c>
-      <c r="AA24" s="11">
-        <f t="shared" si="8"/>
-        <v>423.31632653061223</v>
-      </c>
       <c r="AB24" s="11">
-        <f t="shared" si="9"/>
-        <v>42.33163265306122</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>600.53854875283446</v>
+      </c>
+      <c r="AC24" s="11">
+        <f t="shared" si="11"/>
+        <v>60.053854875283449</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>55</v>
       </c>
@@ -3495,7 +3590,7 @@
         <v>5</v>
       </c>
       <c r="G25" s="4">
-        <f>F25/SUMIFS($F:$F,$A:$A,A25,$B:$B,B25)</f>
+        <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
       <c r="H25" s="3" t="b">
@@ -3535,47 +3630,51 @@
         <v>10</v>
       </c>
       <c r="S25">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <f t="shared" si="1"/>
+        <v>180</v>
       </c>
       <c r="T25">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="V25">
-        <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="W25">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X25">
+        <v>246.91358024691357</v>
+      </c>
+      <c r="W25" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X25" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
       <c r="Z25">
-        <f t="shared" si="7"/>
-        <v>80</v>
-      </c>
-      <c r="AA25" s="11">
         <f t="shared" si="8"/>
-        <v>716.66666666666663</v>
+        <v>60</v>
+      </c>
+      <c r="AA25">
+        <f t="shared" si="9"/>
+        <v>80</v>
       </c>
       <c r="AB25" s="11">
-        <f t="shared" si="9"/>
-        <v>71.666666666666657</v>
-      </c>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1035.2469135802471</v>
+      </c>
+      <c r="AC25" s="11">
+        <f t="shared" si="11"/>
+        <v>103.52469135802471</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>55</v>
       </c>
@@ -3595,7 +3694,7 @@
         <v>35</v>
       </c>
       <c r="G26" s="4">
-        <f>F26/SUMIFS($F:$F,$A:$A,A26,$B:$B,B26)</f>
+        <f t="shared" si="0"/>
         <v>0.35</v>
       </c>
       <c r="H26" s="3" t="b">
@@ -3635,47 +3734,51 @@
         <v>4.166666666666667</v>
       </c>
       <c r="S26">
-        <f t="shared" si="0"/>
-        <v>11.428571428571429</v>
+        <f t="shared" si="1"/>
+        <v>60</v>
       </c>
       <c r="T26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="V26">
+        <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="U26">
-        <f t="shared" si="2"/>
-        <v>80</v>
-      </c>
-      <c r="V26">
-        <f t="shared" si="3"/>
-        <v>50</v>
-      </c>
-      <c r="W26">
-        <f t="shared" si="4"/>
-        <v>33.333333333333336</v>
-      </c>
-      <c r="X26">
+      <c r="W26" s="11">
         <f t="shared" si="5"/>
+        <v>66.666666666666671</v>
+      </c>
+      <c r="X26" s="11">
+        <f t="shared" si="6"/>
         <v>31.25</v>
       </c>
       <c r="Y26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>25</v>
+      </c>
+      <c r="AA26">
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="AA26" s="11">
-        <f t="shared" si="8"/>
-        <v>276.01190476190482</v>
-      </c>
       <c r="AB26" s="11">
-        <f t="shared" si="9"/>
-        <v>27.601190476190482</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>332.91666666666669</v>
+      </c>
+      <c r="AC26" s="11">
+        <f t="shared" si="11"/>
+        <v>33.291666666666671</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>55</v>
       </c>
@@ -3695,7 +3798,7 @@
         <v>1</v>
       </c>
       <c r="G27" s="4">
-        <f>F27/SUMIFS($F:$F,$A:$A,A27,$B:$B,B27)</f>
+        <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
       <c r="H27" s="3" t="b">
@@ -3735,47 +3838,51 @@
         <v>12.5</v>
       </c>
       <c r="S27">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <f t="shared" si="1"/>
+        <v>196</v>
       </c>
       <c r="T27">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>120</v>
       </c>
       <c r="V27">
-        <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="W27">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X27">
+        <v>246.91358024691357</v>
+      </c>
+      <c r="W27" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X27" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>37.5</v>
       </c>
       <c r="Z27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>75</v>
       </c>
-      <c r="AA27" s="11">
-        <f t="shared" si="8"/>
-        <v>1084.1666666666665</v>
+      <c r="AA27">
+        <f t="shared" si="9"/>
+        <v>75</v>
       </c>
       <c r="AB27" s="11">
-        <f t="shared" si="9"/>
-        <v>108.41666666666666</v>
-      </c>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1113.7469135802471</v>
+      </c>
+      <c r="AC27" s="11">
+        <f t="shared" si="11"/>
+        <v>111.37469135802471</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>55</v>
       </c>
@@ -3795,7 +3902,7 @@
         <v>45</v>
       </c>
       <c r="G28" s="4">
-        <f>F28/SUMIFS($F:$F,$A:$A,A28,$B:$B,B28)</f>
+        <f t="shared" si="0"/>
         <v>0.45</v>
       </c>
       <c r="H28" s="3" t="b">
@@ -3835,47 +3942,51 @@
         <v>11.666666666666666</v>
       </c>
       <c r="S28">
-        <f t="shared" si="0"/>
-        <v>8.8888888888888893</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="T28">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>120</v>
       </c>
       <c r="V28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
+        <v>78.124999999999986</v>
+      </c>
+      <c r="W28" s="11">
+        <f t="shared" si="5"/>
+        <v>66.666666666666671</v>
+      </c>
+      <c r="X28" s="11">
+        <f t="shared" si="6"/>
+        <v>80</v>
+      </c>
+      <c r="Y28">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <f t="shared" si="8"/>
         <v>70</v>
       </c>
-      <c r="W28">
-        <f t="shared" si="4"/>
-        <v>33.333333333333336</v>
-      </c>
-      <c r="X28">
-        <f t="shared" si="5"/>
-        <v>80</v>
-      </c>
-      <c r="Y28">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <f t="shared" si="7"/>
+      <c r="AA28">
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="AA28" s="11">
-        <f t="shared" si="8"/>
-        <v>372.22222222222223</v>
-      </c>
       <c r="AB28" s="11">
-        <f t="shared" si="9"/>
-        <v>37.222222222222221</v>
-      </c>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>444.79166666666669</v>
+      </c>
+      <c r="AC28" s="11">
+        <f t="shared" si="11"/>
+        <v>44.479166666666671</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>55</v>
       </c>
@@ -3895,7 +4006,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="4">
-        <f>F29/SUMIFS($F:$F,$A:$A,A29,$B:$B,B29)</f>
+        <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
       <c r="H29" s="3" t="b">
@@ -3935,47 +4046,51 @@
         <v>14.583333333333334</v>
       </c>
       <c r="S29">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <f t="shared" si="1"/>
+        <v>180</v>
       </c>
       <c r="T29">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="V29">
-        <f t="shared" si="3"/>
-        <v>90</v>
-      </c>
-      <c r="W29">
         <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="X29">
+        <v>138.88888888888889</v>
+      </c>
+      <c r="W29" s="11">
         <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
+      <c r="X29" s="11">
+        <f t="shared" si="6"/>
         <v>98.76543209876543</v>
       </c>
       <c r="Y29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="Z29">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>87.5</v>
+      </c>
+      <c r="AA29">
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="AA29" s="11">
-        <f t="shared" si="8"/>
-        <v>613.76543209876547</v>
-      </c>
       <c r="AB29" s="11">
-        <f t="shared" si="9"/>
-        <v>61.376543209876544</v>
-      </c>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>840.15432098765439</v>
+      </c>
+      <c r="AC29" s="11">
+        <f t="shared" si="11"/>
+        <v>84.015432098765444</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>55</v>
       </c>
@@ -3995,7 +4110,7 @@
         <v>5</v>
       </c>
       <c r="G30" s="4">
-        <f>F30/SUMIFS($F:$F,$A:$A,A30,$B:$B,B30)</f>
+        <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
       <c r="H30" s="3" t="b">
@@ -4035,47 +4150,51 @@
         <v>12.5</v>
       </c>
       <c r="S30">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <f t="shared" si="1"/>
+        <v>180</v>
       </c>
       <c r="T30">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="V30">
-        <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="W30">
         <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="X30">
+        <v>246.91358024691357</v>
+      </c>
+      <c r="W30" s="11">
         <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
+      <c r="X30" s="11">
+        <f t="shared" si="6"/>
         <v>98.76543209876543</v>
       </c>
       <c r="Y30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="Z30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>75</v>
+      </c>
+      <c r="AA30">
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="AA30" s="11">
-        <f t="shared" si="8"/>
-        <v>618.76543209876547</v>
-      </c>
       <c r="AB30" s="11">
-        <f t="shared" si="9"/>
-        <v>61.876543209876544</v>
-      </c>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>925.6790123456791</v>
+      </c>
+      <c r="AC30" s="11">
+        <f t="shared" si="11"/>
+        <v>92.567901234567913</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>55</v>
       </c>
@@ -4095,7 +4214,7 @@
         <v>45</v>
       </c>
       <c r="G31" s="4">
-        <f>F31/SUMIFS($F:$F,$A:$A,A31,$B:$B,B31)</f>
+        <f t="shared" si="0"/>
         <v>0.45</v>
       </c>
       <c r="H31" s="3" t="b">
@@ -4135,47 +4254,51 @@
         <v>7.5</v>
       </c>
       <c r="S31">
-        <f t="shared" si="0"/>
-        <v>8.8888888888888893</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="T31">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="V31">
-        <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="W31">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X31">
+        <v>246.91358024691357</v>
+      </c>
+      <c r="W31" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X31" s="11">
+        <f t="shared" si="6"/>
         <v>55.555555555555557</v>
       </c>
       <c r="Y31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12.5</v>
       </c>
       <c r="Z31">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>45</v>
+      </c>
+      <c r="AA31">
+        <f t="shared" si="9"/>
         <v>65</v>
       </c>
-      <c r="AA31" s="11">
-        <f t="shared" si="8"/>
-        <v>453.61111111111109</v>
-      </c>
       <c r="AB31" s="11">
-        <f t="shared" si="9"/>
-        <v>45.361111111111107</v>
-      </c>
-    </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>668.30246913580243</v>
+      </c>
+      <c r="AC31" s="11">
+        <f t="shared" si="11"/>
+        <v>66.83024691358024</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>55</v>
       </c>
@@ -4195,7 +4318,7 @@
         <v>45</v>
       </c>
       <c r="G32" s="4">
-        <f>F32/SUMIFS($F:$F,$A:$A,A32,$B:$B,B32)</f>
+        <f t="shared" si="0"/>
         <v>0.45</v>
       </c>
       <c r="H32" s="3" t="b">
@@ -4235,47 +4358,51 @@
         <v>6.25</v>
       </c>
       <c r="S32">
-        <f t="shared" si="0"/>
-        <v>8.8888888888888893</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="T32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="U32">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
       <c r="V32">
-        <f t="shared" si="3"/>
-        <v>90</v>
-      </c>
-      <c r="W32">
         <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="X32">
+        <v>138.88888888888889</v>
+      </c>
+      <c r="W32" s="11">
         <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="X32" s="11">
+        <f t="shared" si="6"/>
         <v>35.555555555555557</v>
       </c>
       <c r="Y32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="Z32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>37.5</v>
+      </c>
+      <c r="AA32">
+        <f t="shared" si="9"/>
         <v>25</v>
       </c>
-      <c r="AA32" s="11">
-        <f t="shared" si="8"/>
-        <v>314.44444444444446</v>
-      </c>
       <c r="AB32" s="11">
-        <f t="shared" si="9"/>
-        <v>31.444444444444446</v>
-      </c>
-    </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>411.94444444444446</v>
+      </c>
+      <c r="AC32" s="11">
+        <f t="shared" si="11"/>
+        <v>41.194444444444443</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>55</v>
       </c>
@@ -4295,7 +4422,7 @@
         <v>13</v>
       </c>
       <c r="G33" s="4">
-        <f>F33/SUMIFS($F:$F,$A:$A,A33,$B:$B,B33)</f>
+        <f t="shared" si="0"/>
         <v>0.13</v>
       </c>
       <c r="H33" s="3" t="b">
@@ -4335,47 +4462,51 @@
         <v>9.1666666666666661</v>
       </c>
       <c r="S33">
-        <f t="shared" si="0"/>
-        <v>30.76923076923077</v>
+        <f t="shared" si="1"/>
+        <v>148</v>
       </c>
       <c r="T33">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="V33">
-        <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="W33">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X33">
+        <v>246.91358024691357</v>
+      </c>
+      <c r="W33" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X33" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12.5</v>
       </c>
       <c r="Z33">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>55</v>
+      </c>
+      <c r="AA33">
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
-      <c r="AA33" s="11">
-        <f t="shared" si="8"/>
-        <v>604.93589743589746</v>
-      </c>
       <c r="AB33" s="11">
-        <f t="shared" si="9"/>
-        <v>60.493589743589745</v>
-      </c>
-    </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>935.746913580247</v>
+      </c>
+      <c r="AC33" s="11">
+        <f t="shared" si="11"/>
+        <v>93.574691358024694</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>55</v>
       </c>
@@ -4395,7 +4526,7 @@
         <v>2</v>
       </c>
       <c r="G34" s="4">
-        <f>F34/SUMIFS($F:$F,$A:$A,A34,$B:$B,B34)</f>
+        <f t="shared" ref="G34:G65" si="12">F34/SUMIFS($F:$F,$A:$A,A34,$B:$B,B34)</f>
         <v>0.02</v>
       </c>
       <c r="H34" s="3" t="b">
@@ -4435,47 +4566,51 @@
         <v>11.666666666666666</v>
       </c>
       <c r="S34">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <f t="shared" si="1"/>
+        <v>192</v>
       </c>
       <c r="T34">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="V34">
-        <f t="shared" si="3"/>
-        <v>110</v>
-      </c>
-      <c r="W34">
         <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="X34">
+        <v>312.49999999999994</v>
+      </c>
+      <c r="W34" s="11">
         <f t="shared" si="5"/>
         <v>80</v>
       </c>
+      <c r="X34" s="11">
+        <f t="shared" si="6"/>
+        <v>80</v>
+      </c>
       <c r="Y34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>37.5</v>
       </c>
       <c r="Z34">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>70</v>
+      </c>
+      <c r="AA34">
+        <f t="shared" si="9"/>
         <v>60</v>
       </c>
-      <c r="AA34" s="11">
-        <f t="shared" si="8"/>
-        <v>817.5</v>
-      </c>
       <c r="AB34" s="11">
-        <f t="shared" si="9"/>
-        <v>81.75</v>
-      </c>
-    </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1072</v>
+      </c>
+      <c r="AC34" s="11">
+        <f t="shared" si="11"/>
+        <v>107.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>55</v>
       </c>
@@ -4495,7 +4630,7 @@
         <v>35</v>
       </c>
       <c r="G35" s="4">
-        <f>F35/SUMIFS($F:$F,$A:$A,A35,$B:$B,B35)</f>
+        <f t="shared" si="12"/>
         <v>0.35</v>
       </c>
       <c r="H35" s="3" t="b">
@@ -4535,47 +4670,51 @@
         <v>7.5</v>
       </c>
       <c r="S35">
-        <f t="shared" si="0"/>
-        <v>11.428571428571429</v>
+        <f t="shared" si="1"/>
+        <v>60</v>
       </c>
       <c r="T35">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="V35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
+        <v>200</v>
+      </c>
+      <c r="W35" s="11">
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="W35">
-        <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="X35">
-        <f t="shared" si="5"/>
+      <c r="X35" s="11">
+        <f t="shared" si="6"/>
         <v>40.816326530612244</v>
       </c>
       <c r="Y35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12.5</v>
       </c>
       <c r="Z35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
-      <c r="AA35" s="11">
-        <f t="shared" si="8"/>
-        <v>379.74489795918367</v>
+      <c r="AA35">
+        <f t="shared" si="9"/>
+        <v>45</v>
       </c>
       <c r="AB35" s="11">
-        <f t="shared" si="9"/>
-        <v>37.974489795918366</v>
-      </c>
-    </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>573.31632653061229</v>
+      </c>
+      <c r="AC35" s="11">
+        <f t="shared" si="11"/>
+        <v>57.331632653061227</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>55</v>
       </c>
@@ -4595,7 +4734,7 @@
         <v>5</v>
       </c>
       <c r="G36" s="4">
-        <f>F36/SUMIFS($F:$F,$A:$A,A36,$B:$B,B36)</f>
+        <f t="shared" si="12"/>
         <v>0.05</v>
       </c>
       <c r="H36" s="3" t="b">
@@ -4635,47 +4774,51 @@
         <v>11.666666666666666</v>
       </c>
       <c r="S36">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <f t="shared" si="1"/>
+        <v>180</v>
       </c>
       <c r="T36">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="V36">
-        <f t="shared" si="3"/>
-        <v>110</v>
-      </c>
-      <c r="W36">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X36">
+        <v>312.49999999999994</v>
+      </c>
+      <c r="W36" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X36" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>35</v>
       </c>
       <c r="Z36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>70</v>
+      </c>
+      <c r="AA36">
+        <f t="shared" si="9"/>
         <v>60</v>
       </c>
-      <c r="AA36" s="11">
-        <f t="shared" si="8"/>
-        <v>691.66666666666663</v>
-      </c>
       <c r="AB36" s="11">
-        <f t="shared" si="9"/>
-        <v>69.166666666666657</v>
-      </c>
-    </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1080.8333333333335</v>
+      </c>
+      <c r="AC36" s="11">
+        <f t="shared" si="11"/>
+        <v>108.08333333333334</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>94</v>
       </c>
@@ -4695,7 +4838,7 @@
         <v>20</v>
       </c>
       <c r="G37" s="4">
-        <f>F37/SUMIFS($F:$F,$A:$A,A37,$B:$B,B37)</f>
+        <f t="shared" si="12"/>
         <v>0.4</v>
       </c>
       <c r="H37" s="3" t="b">
@@ -4735,47 +4878,51 @@
         <v>7.5</v>
       </c>
       <c r="S37">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>120</v>
       </c>
       <c r="T37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="U37">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
       <c r="V37">
-        <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="W37">
         <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="X37">
+        <v>165.28925619834709</v>
+      </c>
+      <c r="W37" s="11">
         <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="X37" s="11">
+        <f t="shared" si="6"/>
         <v>35.555555555555557</v>
       </c>
       <c r="Y37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z37">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>45</v>
+      </c>
+      <c r="AA37">
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
-      <c r="AA37" s="11">
-        <f t="shared" si="8"/>
-        <v>330.55555555555554</v>
-      </c>
       <c r="AB37" s="11">
-        <f t="shared" si="9"/>
-        <v>33.055555555555557</v>
-      </c>
-    </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>545.8448117539026</v>
+      </c>
+      <c r="AC37" s="11">
+        <f t="shared" si="11"/>
+        <v>54.584481175390259</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>94</v>
       </c>
@@ -4795,7 +4942,7 @@
         <v>3</v>
       </c>
       <c r="G38" s="4">
-        <f>F38/SUMIFS($F:$F,$A:$A,A38,$B:$B,B38)</f>
+        <f t="shared" si="12"/>
         <v>0.06</v>
       </c>
       <c r="H38" s="3" t="b">
@@ -4835,47 +4982,51 @@
         <v>9.5833333333333339</v>
       </c>
       <c r="S38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
+        <v>188</v>
+      </c>
+      <c r="T38">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="V38">
+        <f t="shared" si="4"/>
+        <v>200</v>
+      </c>
+      <c r="W38" s="11">
+        <f t="shared" si="5"/>
         <v>133.33333333333334</v>
       </c>
-      <c r="T38">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="U38">
-        <f t="shared" si="2"/>
-        <v>80</v>
-      </c>
-      <c r="V38">
-        <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-      <c r="W38">
-        <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X38">
-        <f t="shared" si="5"/>
+      <c r="X38" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y38">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="Z38">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>57.5</v>
+      </c>
+      <c r="AA38">
+        <f t="shared" si="9"/>
         <v>37.5</v>
       </c>
-      <c r="AA38" s="11">
-        <f t="shared" si="8"/>
-        <v>557.5</v>
-      </c>
       <c r="AB38" s="11">
-        <f t="shared" si="9"/>
-        <v>55.75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>786.33333333333337</v>
+      </c>
+      <c r="AC38" s="11">
+        <f t="shared" si="11"/>
+        <v>78.63333333333334</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>94</v>
       </c>
@@ -4895,7 +5046,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="4">
-        <f>F39/SUMIFS($F:$F,$A:$A,A39,$B:$B,B39)</f>
+        <f t="shared" si="12"/>
         <v>0.02</v>
       </c>
       <c r="H39" s="3" t="b">
@@ -4935,47 +5086,51 @@
         <v>10.833333333333334</v>
       </c>
       <c r="S39">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <f t="shared" si="1"/>
+        <v>196</v>
       </c>
       <c r="T39">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="V39">
-        <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="W39">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X39">
+        <v>246.91358024691357</v>
+      </c>
+      <c r="W39" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X39" s="11">
+        <f t="shared" si="6"/>
         <v>125</v>
       </c>
       <c r="Y39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="Z39">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>65</v>
+      </c>
+      <c r="AA39">
+        <f t="shared" si="9"/>
         <v>50</v>
       </c>
-      <c r="AA39" s="11">
-        <f t="shared" si="8"/>
-        <v>1026.6666666666665</v>
-      </c>
       <c r="AB39" s="11">
-        <f t="shared" si="9"/>
-        <v>102.66666666666666</v>
-      </c>
-    </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1046.2469135802471</v>
+      </c>
+      <c r="AC39" s="11">
+        <f t="shared" si="11"/>
+        <v>104.62469135802471</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>94</v>
       </c>
@@ -4995,7 +5150,7 @@
         <v>1</v>
       </c>
       <c r="G40" s="4">
-        <f>F40/SUMIFS($F:$F,$A:$A,A40,$B:$B,B40)</f>
+        <f t="shared" si="12"/>
         <v>0.02</v>
       </c>
       <c r="H40" s="3" t="b">
@@ -5035,47 +5190,51 @@
         <v>12.5</v>
       </c>
       <c r="S40">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <f t="shared" si="1"/>
+        <v>196</v>
       </c>
       <c r="T40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+      <c r="U40">
+        <f t="shared" si="3"/>
+        <v>70</v>
+      </c>
+      <c r="V40">
+        <f t="shared" si="4"/>
         <v>200</v>
       </c>
-      <c r="U40">
-        <f t="shared" si="2"/>
-        <v>70</v>
-      </c>
-      <c r="V40">
-        <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-      <c r="W40">
-        <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X40">
+      <c r="W40" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X40" s="11">
+        <f t="shared" si="6"/>
         <v>125</v>
       </c>
       <c r="Y40">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
       <c r="Z40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>75</v>
+      </c>
+      <c r="AA40">
+        <f t="shared" si="9"/>
         <v>60</v>
       </c>
-      <c r="AA40" s="11">
-        <f t="shared" si="8"/>
-        <v>1046.6666666666665</v>
-      </c>
       <c r="AB40" s="11">
-        <f t="shared" si="9"/>
-        <v>104.66666666666666</v>
-      </c>
-    </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1034.3333333333335</v>
+      </c>
+      <c r="AC40" s="11">
+        <f t="shared" si="11"/>
+        <v>103.43333333333335</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>94</v>
       </c>
@@ -5095,7 +5254,7 @@
         <v>20</v>
       </c>
       <c r="G41" s="4">
-        <f>F41/SUMIFS($F:$F,$A:$A,A41,$B:$B,B41)</f>
+        <f t="shared" si="12"/>
         <v>0.4</v>
       </c>
       <c r="H41" s="3" t="b">
@@ -5135,47 +5294,51 @@
         <v>5.833333333333333</v>
       </c>
       <c r="S41">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>120</v>
       </c>
       <c r="T41">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="V41">
-        <f t="shared" si="3"/>
-        <v>75</v>
-      </c>
-      <c r="W41">
         <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="X41">
+        <v>88.888888888888886</v>
+      </c>
+      <c r="W41" s="11">
         <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="X41" s="11">
+        <f t="shared" si="6"/>
         <v>31.25</v>
       </c>
       <c r="Y41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>35</v>
       </c>
-      <c r="AA41" s="11">
-        <f t="shared" si="8"/>
-        <v>331.25</v>
+      <c r="AA41">
+        <f t="shared" si="9"/>
+        <v>35</v>
       </c>
       <c r="AB41" s="11">
-        <f t="shared" si="9"/>
-        <v>33.125</v>
-      </c>
-    </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>480.13888888888891</v>
+      </c>
+      <c r="AC41" s="11">
+        <f t="shared" si="11"/>
+        <v>48.013888888888893</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>94</v>
       </c>
@@ -5195,7 +5358,7 @@
         <v>5</v>
       </c>
       <c r="G42" s="4">
-        <f>F42/SUMIFS($F:$F,$A:$A,A42,$B:$B,B42)</f>
+        <f t="shared" si="12"/>
         <v>0.1</v>
       </c>
       <c r="H42" s="3" t="b">
@@ -5235,47 +5398,51 @@
         <v>10</v>
       </c>
       <c r="S42">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <f t="shared" si="1"/>
+        <v>180</v>
       </c>
       <c r="T42">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="V42">
-        <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="W42">
         <f t="shared" si="4"/>
+        <v>165.28925619834709</v>
+      </c>
+      <c r="W42" s="11">
+        <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
+      <c r="X42" s="11">
+        <f t="shared" si="6"/>
+        <v>55.555555555555557</v>
+      </c>
+      <c r="Y42">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="Z42">
+        <f t="shared" si="8"/>
+        <v>60</v>
+      </c>
+      <c r="AA42">
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
-      <c r="X42">
-        <f t="shared" si="5"/>
-        <v>55.555555555555557</v>
-      </c>
-      <c r="Y42">
-        <f t="shared" si="6"/>
-        <v>20</v>
-      </c>
-      <c r="Z42">
-        <f t="shared" si="7"/>
-        <v>40</v>
-      </c>
-      <c r="AA42" s="11">
-        <f t="shared" si="8"/>
-        <v>580.55555555555554</v>
-      </c>
       <c r="AB42" s="11">
-        <f t="shared" si="9"/>
-        <v>58.055555555555557</v>
-      </c>
-    </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>800.8448117539026</v>
+      </c>
+      <c r="AC42" s="11">
+        <f t="shared" si="11"/>
+        <v>80.084481175390266</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>94</v>
       </c>
@@ -5295,7 +5462,7 @@
         <v>21</v>
       </c>
       <c r="G43" s="4">
-        <f>F43/SUMIFS($F:$F,$A:$A,A43,$B:$B,B43)</f>
+        <f t="shared" si="12"/>
         <v>0.36842105263157893</v>
       </c>
       <c r="H43" s="3" t="b">
@@ -5335,47 +5502,51 @@
         <v>5.833333333333333</v>
       </c>
       <c r="S43">
-        <f t="shared" si="0"/>
-        <v>19.047619047619047</v>
+        <f t="shared" si="1"/>
+        <v>116</v>
       </c>
       <c r="T43">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="V43">
-        <f t="shared" si="3"/>
-        <v>90</v>
-      </c>
-      <c r="W43">
         <f t="shared" si="4"/>
-        <v>33.333333333333336</v>
-      </c>
-      <c r="X43">
+        <v>138.88888888888889</v>
+      </c>
+      <c r="W43" s="11">
         <f t="shared" si="5"/>
+        <v>66.666666666666671</v>
+      </c>
+      <c r="X43" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>35</v>
+      </c>
+      <c r="AA43">
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="AA43" s="11">
-        <f t="shared" si="8"/>
-        <v>372.38095238095235</v>
-      </c>
       <c r="AB43" s="11">
-        <f t="shared" si="9"/>
-        <v>37.238095238095234</v>
-      </c>
-    </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>536.55555555555566</v>
+      </c>
+      <c r="AC43" s="11">
+        <f t="shared" si="11"/>
+        <v>53.655555555555566</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>94</v>
       </c>
@@ -5395,7 +5566,7 @@
         <v>5</v>
       </c>
       <c r="G44" s="4">
-        <f>F44/SUMIFS($F:$F,$A:$A,A44,$B:$B,B44)</f>
+        <f t="shared" si="12"/>
         <v>8.771929824561403E-2</v>
       </c>
       <c r="H44" s="3" t="b">
@@ -5435,47 +5606,51 @@
         <v>9.1666666666666661</v>
       </c>
       <c r="S44">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <f t="shared" si="1"/>
+        <v>180</v>
       </c>
       <c r="T44">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>120</v>
       </c>
       <c r="V44">
-        <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-      <c r="W44">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X44">
+        <v>200</v>
+      </c>
+      <c r="W44" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X44" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12.5</v>
       </c>
       <c r="Z44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>55</v>
+      </c>
+      <c r="AA44">
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
-      <c r="AA44" s="11">
-        <f t="shared" si="8"/>
-        <v>549.16666666666674</v>
-      </c>
       <c r="AB44" s="11">
-        <f t="shared" si="9"/>
-        <v>54.916666666666671</v>
-      </c>
-    </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>820.83333333333337</v>
+      </c>
+      <c r="AC44" s="11">
+        <f t="shared" si="11"/>
+        <v>82.083333333333343</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>94</v>
       </c>
@@ -5495,7 +5670,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="4">
-        <f>F45/SUMIFS($F:$F,$A:$A,A45,$B:$B,B45)</f>
+        <f t="shared" si="12"/>
         <v>1.7543859649122806E-2</v>
       </c>
       <c r="H45" s="3" t="b">
@@ -5535,47 +5710,51 @@
         <v>20.833333333333332</v>
       </c>
       <c r="S45">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <f t="shared" si="1"/>
+        <v>196</v>
       </c>
       <c r="T45">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100</v>
       </c>
       <c r="V45">
-        <f t="shared" si="3"/>
-        <v>110</v>
-      </c>
-      <c r="W45">
         <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="X45">
+        <v>312.49999999999994</v>
+      </c>
+      <c r="W45" s="11">
         <f t="shared" si="5"/>
+        <v>40</v>
+      </c>
+      <c r="X45" s="11">
+        <f t="shared" si="6"/>
         <v>163.26530612244898</v>
       </c>
       <c r="Y45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
       <c r="Z45">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>125</v>
+      </c>
+      <c r="AA45">
+        <f t="shared" si="9"/>
         <v>50</v>
       </c>
-      <c r="AA45" s="11">
-        <f t="shared" si="8"/>
-        <v>1068.2653061224489</v>
-      </c>
       <c r="AB45" s="11">
-        <f t="shared" si="9"/>
-        <v>106.82653061224489</v>
-      </c>
-    </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1161.7653061224489</v>
+      </c>
+      <c r="AC45" s="11">
+        <f t="shared" si="11"/>
+        <v>116.17653061224489</v>
+      </c>
+    </row>
+    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>94</v>
       </c>
@@ -5595,7 +5774,7 @@
         <v>25</v>
       </c>
       <c r="G46" s="4">
-        <f>F46/SUMIFS($F:$F,$A:$A,A46,$B:$B,B46)</f>
+        <f t="shared" si="12"/>
         <v>0.43859649122807015</v>
       </c>
       <c r="H46" s="3" t="b">
@@ -5635,47 +5814,51 @@
         <v>7.5</v>
       </c>
       <c r="S46">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="T46">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="V46">
-        <f t="shared" si="3"/>
-        <v>90</v>
-      </c>
-      <c r="W46">
         <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="X46">
+        <v>138.88888888888889</v>
+      </c>
+      <c r="W46" s="11">
         <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
+      <c r="X46" s="11">
+        <f t="shared" si="6"/>
         <v>40.816326530612244</v>
       </c>
       <c r="Y46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="Z46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>45</v>
+      </c>
+      <c r="AA46">
+        <f t="shared" si="9"/>
         <v>37.5</v>
       </c>
-      <c r="AA46" s="11">
-        <f t="shared" si="8"/>
-        <v>349.31632653061223</v>
-      </c>
       <c r="AB46" s="11">
-        <f t="shared" si="9"/>
-        <v>34.931632653061222</v>
-      </c>
-    </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>517.2052154195012</v>
+      </c>
+      <c r="AC46" s="11">
+        <f t="shared" si="11"/>
+        <v>51.72052154195012</v>
+      </c>
+    </row>
+    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>94</v>
       </c>
@@ -5695,7 +5878,7 @@
         <v>5</v>
       </c>
       <c r="G47" s="4">
-        <f>F47/SUMIFS($F:$F,$A:$A,A47,$B:$B,B47)</f>
+        <f t="shared" si="12"/>
         <v>8.771929824561403E-2</v>
       </c>
       <c r="H47" s="3" t="b">
@@ -5735,47 +5918,51 @@
         <v>10</v>
       </c>
       <c r="S47">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <f t="shared" si="1"/>
+        <v>180</v>
       </c>
       <c r="T47">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U47">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="V47">
-        <f t="shared" si="3"/>
-        <v>102.5</v>
-      </c>
-      <c r="W47">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X47">
+        <v>221.606648199446</v>
+      </c>
+      <c r="W47" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X47" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="Z47">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>60</v>
+      </c>
+      <c r="AA47">
+        <f t="shared" si="9"/>
         <v>55</v>
       </c>
-      <c r="AA47" s="11">
-        <f t="shared" si="8"/>
-        <v>674.16666666666663</v>
-      </c>
       <c r="AB47" s="11">
-        <f t="shared" si="9"/>
-        <v>67.416666666666657</v>
-      </c>
-    </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>969.93998153277937</v>
+      </c>
+      <c r="AC47" s="11">
+        <f t="shared" si="11"/>
+        <v>96.993998153277943</v>
+      </c>
+    </row>
+    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>94</v>
       </c>
@@ -5792,11 +5979,10 @@
         <v>118</v>
       </c>
       <c r="F48" s="3">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="G48" s="4">
-        <f>F48/SUMIFS($F:$F,$A:$A,A48,$B:$B,B48)</f>
-        <v>0.7142857142857143</v>
+        <v>0.45</v>
       </c>
       <c r="H48" s="3" t="b">
         <v>0</v>
@@ -5835,47 +6021,51 @@
         <v>6.666666666666667</v>
       </c>
       <c r="S48">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="T48">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U48">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="V48">
-        <f t="shared" si="3"/>
-        <v>90</v>
-      </c>
-      <c r="W48">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X48">
+        <v>138.88888888888889</v>
+      </c>
+      <c r="W48" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X48" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y48">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="Z48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>40</v>
+      </c>
+      <c r="AA48">
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="AA48" s="11">
-        <f t="shared" si="8"/>
-        <v>385.66666666666669</v>
-      </c>
       <c r="AB48" s="11">
-        <f t="shared" si="9"/>
-        <v>38.56666666666667</v>
-      </c>
-    </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>507.22222222222223</v>
+      </c>
+      <c r="AC48" s="11">
+        <f t="shared" si="11"/>
+        <v>50.722222222222221</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>94</v>
       </c>
@@ -5895,8 +6085,8 @@
         <v>10</v>
       </c>
       <c r="G49" s="4">
-        <f>F49/SUMIFS($F:$F,$A:$A,A49,$B:$B,B49)</f>
-        <v>7.1428571428571425E-2</v>
+        <f t="shared" si="12"/>
+        <v>0.11764705882352941</v>
       </c>
       <c r="H49" s="3" t="b">
         <v>1</v>
@@ -5935,47 +6125,51 @@
         <v>10.833333333333334</v>
       </c>
       <c r="S49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="T49">
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+      <c r="U49">
+        <f t="shared" si="3"/>
+        <v>90</v>
+      </c>
+      <c r="V49">
+        <f t="shared" si="4"/>
+        <v>246.91358024691357</v>
+      </c>
+      <c r="W49" s="11">
+        <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
+      <c r="X49" s="11">
+        <f t="shared" si="6"/>
+        <v>98.76543209876543</v>
+      </c>
+      <c r="Y49">
+        <f t="shared" si="7"/>
+        <v>30</v>
+      </c>
+      <c r="Z49">
+        <f t="shared" si="8"/>
+        <v>65</v>
+      </c>
+      <c r="AA49">
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
-      <c r="T49">
-        <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="U49">
-        <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-      <c r="V49">
-        <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="W49">
-        <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="X49">
-        <f t="shared" si="5"/>
-        <v>98.76543209876543</v>
-      </c>
-      <c r="Y49">
-        <f t="shared" si="6"/>
-        <v>30</v>
-      </c>
-      <c r="Z49">
-        <f t="shared" si="7"/>
-        <v>40</v>
-      </c>
-      <c r="AA49" s="11">
-        <f t="shared" si="8"/>
-        <v>643.76543209876547</v>
-      </c>
       <c r="AB49" s="11">
-        <f t="shared" si="9"/>
-        <v>64.376543209876544</v>
-      </c>
-    </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>960.6790123456791</v>
+      </c>
+      <c r="AC49" s="11">
+        <f t="shared" si="11"/>
+        <v>96.067901234567913</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>94</v>
       </c>
@@ -5995,8 +6189,8 @@
         <v>10</v>
       </c>
       <c r="G50" s="4">
-        <f>F50/SUMIFS($F:$F,$A:$A,A50,$B:$B,B50)</f>
-        <v>7.1428571428571425E-2</v>
+        <f t="shared" si="12"/>
+        <v>0.11764705882352941</v>
       </c>
       <c r="H50" s="3" t="b">
         <v>0</v>
@@ -6035,47 +6229,51 @@
         <v>5.833333333333333</v>
       </c>
       <c r="S50">
-        <f t="shared" si="0"/>
-        <v>40</v>
+        <f t="shared" si="1"/>
+        <v>160</v>
       </c>
       <c r="T50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="U50">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
       <c r="V50">
-        <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="W50">
         <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="X50">
+        <v>102.04081632653063</v>
+      </c>
+      <c r="W50" s="11">
         <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
+      <c r="X50" s="11">
+        <f t="shared" si="6"/>
         <v>55.555555555555557</v>
       </c>
       <c r="Y50">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z50">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>35</v>
+      </c>
+      <c r="AA50">
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="AA50" s="11">
-        <f t="shared" si="8"/>
-        <v>330.55555555555554</v>
-      </c>
       <c r="AB50" s="11">
-        <f t="shared" si="9"/>
-        <v>33.055555555555557</v>
-      </c>
-    </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>497.59637188208615</v>
+      </c>
+      <c r="AC50" s="11">
+        <f t="shared" si="11"/>
+        <v>49.759637188208615</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>94</v>
       </c>
@@ -6095,8 +6293,8 @@
         <v>10</v>
       </c>
       <c r="G51" s="4">
-        <f>F51/SUMIFS($F:$F,$A:$A,A51,$B:$B,B51)</f>
-        <v>7.1428571428571425E-2</v>
+        <f t="shared" si="12"/>
+        <v>0.11764705882352941</v>
       </c>
       <c r="H51" s="3" t="b">
         <v>1</v>
@@ -6135,47 +6333,51 @@
         <v>9.1666666666666661</v>
       </c>
       <c r="S51">
-        <f t="shared" si="0"/>
-        <v>40</v>
+        <f t="shared" si="1"/>
+        <v>160</v>
       </c>
       <c r="T51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+      <c r="U51">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="V51">
+        <f t="shared" si="4"/>
         <v>200</v>
       </c>
-      <c r="U51">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="V51">
-        <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-      <c r="W51">
-        <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X51">
+      <c r="W51" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X51" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12.5</v>
       </c>
       <c r="Z51">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>55</v>
+      </c>
+      <c r="AA51">
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
-      <c r="AA51" s="11">
-        <f t="shared" si="8"/>
-        <v>579.16666666666674</v>
-      </c>
       <c r="AB51" s="11">
-        <f t="shared" si="9"/>
-        <v>57.916666666666671</v>
-      </c>
-    </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>870.83333333333337</v>
+      </c>
+      <c r="AC51" s="11">
+        <f t="shared" si="11"/>
+        <v>87.083333333333343</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>94</v>
       </c>
@@ -6195,8 +6397,8 @@
         <v>10</v>
       </c>
       <c r="G52" s="4">
-        <f>F52/SUMIFS($F:$F,$A:$A,A52,$B:$B,B52)</f>
-        <v>7.1428571428571425E-2</v>
+        <f t="shared" si="12"/>
+        <v>0.11764705882352941</v>
       </c>
       <c r="H52" s="3" t="b">
         <v>1</v>
@@ -6235,47 +6437,51 @@
         <v>12.5</v>
       </c>
       <c r="S52">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="T52">
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+      <c r="U52">
+        <f t="shared" si="3"/>
+        <v>120</v>
+      </c>
+      <c r="V52">
+        <f t="shared" si="4"/>
+        <v>276.8166089965398</v>
+      </c>
+      <c r="W52" s="11">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="X52" s="11">
+        <f t="shared" si="6"/>
+        <v>125</v>
+      </c>
+      <c r="Y52">
+        <f t="shared" si="7"/>
+        <v>37.5</v>
+      </c>
+      <c r="Z52">
+        <f t="shared" si="8"/>
+        <v>75</v>
+      </c>
+      <c r="AA52">
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
-      <c r="T52">
-        <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="U52">
-        <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="V52">
-        <f t="shared" si="3"/>
-        <v>107.5</v>
-      </c>
-      <c r="W52">
-        <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="X52">
-        <f t="shared" si="5"/>
-        <v>125</v>
-      </c>
-      <c r="Y52">
-        <f t="shared" si="6"/>
-        <v>37.5</v>
-      </c>
-      <c r="Z52">
-        <f t="shared" si="7"/>
-        <v>40</v>
-      </c>
-      <c r="AA52" s="11">
-        <f t="shared" si="8"/>
-        <v>720</v>
-      </c>
       <c r="AB52" s="11">
-        <f t="shared" si="9"/>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1084.3166089965398</v>
+      </c>
+      <c r="AC52" s="11">
+        <f t="shared" si="11"/>
+        <v>108.43166089965398</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>94</v>
       </c>
@@ -6295,7 +6501,7 @@
         <v>20</v>
       </c>
       <c r="G53" s="4">
-        <f>F53/SUMIFS($F:$F,$A:$A,A53,$B:$B,B53)</f>
+        <f t="shared" si="12"/>
         <v>0.44444444444444442</v>
       </c>
       <c r="H53" s="3" t="b">
@@ -6335,47 +6541,51 @@
         <v>7.5</v>
       </c>
       <c r="S53">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="T53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="V53">
+        <f t="shared" si="4"/>
+        <v>165.28925619834709</v>
+      </c>
+      <c r="W53" s="11">
+        <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
+      <c r="X53" s="11">
+        <f t="shared" si="6"/>
+        <v>66.11570247933885</v>
+      </c>
+      <c r="Y53">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z53">
+        <f t="shared" si="8"/>
+        <v>45</v>
+      </c>
+      <c r="AA53">
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="T53">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="U53">
-        <f t="shared" si="2"/>
-        <v>60</v>
-      </c>
-      <c r="V53">
-        <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="W53">
-        <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="X53">
-        <f t="shared" si="5"/>
-        <v>66.11570247933885</v>
-      </c>
-      <c r="Y53">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Z53">
-        <f t="shared" si="7"/>
-        <v>20</v>
-      </c>
-      <c r="AA53" s="11">
-        <f t="shared" si="8"/>
-        <v>351.11570247933884</v>
-      </c>
       <c r="AB53" s="11">
-        <f t="shared" si="9"/>
-        <v>35.111570247933884</v>
-      </c>
-    </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>556.40495867768595</v>
+      </c>
+      <c r="AC53" s="11">
+        <f t="shared" si="11"/>
+        <v>55.640495867768593</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>94</v>
       </c>
@@ -6395,7 +6605,7 @@
         <v>5</v>
       </c>
       <c r="G54" s="4">
-        <f>F54/SUMIFS($F:$F,$A:$A,A54,$B:$B,B54)</f>
+        <f t="shared" si="12"/>
         <v>0.1111111111111111</v>
       </c>
       <c r="H54" s="3" t="b">
@@ -6435,47 +6645,51 @@
         <v>10</v>
       </c>
       <c r="S54">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <f t="shared" si="1"/>
+        <v>180</v>
       </c>
       <c r="T54">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+      <c r="U54">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="V54">
+        <f t="shared" si="4"/>
         <v>200</v>
       </c>
-      <c r="U54">
-        <f t="shared" si="2"/>
-        <v>80</v>
-      </c>
-      <c r="V54">
-        <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-      <c r="W54">
-        <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="X54">
+      <c r="W54" s="11">
         <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
+      <c r="X54" s="11">
+        <f t="shared" si="6"/>
         <v>125</v>
       </c>
       <c r="Y54">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12.5</v>
       </c>
       <c r="Z54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>60</v>
+      </c>
+      <c r="AA54">
+        <f t="shared" si="9"/>
         <v>45</v>
       </c>
-      <c r="AA54" s="11">
-        <f t="shared" si="8"/>
-        <v>682.5</v>
-      </c>
       <c r="AB54" s="11">
-        <f t="shared" si="9"/>
-        <v>68.25</v>
-      </c>
-    </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>932.5</v>
+      </c>
+      <c r="AC54" s="11">
+        <f t="shared" si="11"/>
+        <v>93.25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>94</v>
       </c>
@@ -6495,7 +6709,7 @@
         <v>10</v>
       </c>
       <c r="G55" s="4">
-        <f>F55/SUMIFS($F:$F,$A:$A,A55,$B:$B,B55)</f>
+        <f t="shared" si="12"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="H55" s="3" t="b">
@@ -6535,47 +6749,51 @@
         <v>7.083333333333333</v>
       </c>
       <c r="S55">
-        <f t="shared" si="0"/>
-        <v>40</v>
+        <f t="shared" si="1"/>
+        <v>160</v>
       </c>
       <c r="T55">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U55">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="V55">
-        <f t="shared" si="3"/>
-        <v>90</v>
-      </c>
-      <c r="W55">
         <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="X55">
+        <v>138.88888888888889</v>
+      </c>
+      <c r="W55" s="11">
         <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="X55" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y55">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="Z55">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>42.5</v>
+      </c>
+      <c r="AA55">
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
-      <c r="AA55" s="11">
-        <f t="shared" si="8"/>
-        <v>415</v>
-      </c>
       <c r="AB55" s="11">
-        <f t="shared" si="9"/>
-        <v>41.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>626.38888888888891</v>
+      </c>
+      <c r="AC55" s="11">
+        <f t="shared" si="11"/>
+        <v>62.638888888888893</v>
+      </c>
+    </row>
+    <row r="56" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>94</v>
       </c>
@@ -6595,7 +6813,7 @@
         <v>10</v>
       </c>
       <c r="G56" s="4">
-        <f>F56/SUMIFS($F:$F,$A:$A,A56,$B:$B,B56)</f>
+        <f t="shared" si="12"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="H56" s="3" t="b">
@@ -6635,47 +6853,51 @@
         <v>10.416666666666666</v>
       </c>
       <c r="S56">
-        <f t="shared" si="0"/>
-        <v>40</v>
+        <f t="shared" si="1"/>
+        <v>160</v>
       </c>
       <c r="T56">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="V56">
-        <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="W56">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X56">
+        <v>246.91358024691357</v>
+      </c>
+      <c r="W56" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X56" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
       <c r="Z56">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>62.5</v>
+      </c>
+      <c r="AA56">
+        <f t="shared" si="9"/>
         <v>60</v>
       </c>
-      <c r="AA56" s="11">
-        <f t="shared" si="8"/>
-        <v>646.66666666666674</v>
-      </c>
       <c r="AB56" s="11">
-        <f t="shared" si="9"/>
-        <v>64.666666666666671</v>
-      </c>
-    </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>987.746913580247</v>
+      </c>
+      <c r="AC56" s="11">
+        <f t="shared" si="11"/>
+        <v>98.774691358024697</v>
+      </c>
+    </row>
+    <row r="57" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>135</v>
       </c>
@@ -6695,7 +6917,7 @@
         <v>33</v>
       </c>
       <c r="G57" s="4">
-        <f>F57/SUMIFS($F:$F,$A:$A,A57,$B:$B,B57)</f>
+        <f t="shared" si="12"/>
         <v>0.33</v>
       </c>
       <c r="H57" s="3" t="b">
@@ -6735,47 +6957,51 @@
         <v>7.5</v>
       </c>
       <c r="S57">
-        <f t="shared" si="0"/>
-        <v>12.121212121212121</v>
+        <f t="shared" si="1"/>
+        <v>68</v>
       </c>
       <c r="T57">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U57">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="V57">
-        <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="W57">
         <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="X57">
+        <v>165.28925619834709</v>
+      </c>
+      <c r="W57" s="11">
         <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="X57" s="11">
+        <f t="shared" si="6"/>
         <v>40.816326530612244</v>
       </c>
       <c r="Y57">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.5</v>
       </c>
       <c r="Z57">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>45</v>
+      </c>
+      <c r="AA57">
+        <f t="shared" si="9"/>
         <v>35</v>
       </c>
-      <c r="AA57" s="11">
-        <f t="shared" si="8"/>
-        <v>380.43753865182435</v>
-      </c>
       <c r="AB57" s="11">
-        <f t="shared" si="9"/>
-        <v>38.043753865182438</v>
-      </c>
-    </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>551.60558272895923</v>
+      </c>
+      <c r="AC57" s="11">
+        <f t="shared" si="11"/>
+        <v>55.160558272895926</v>
+      </c>
+    </row>
+    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>135</v>
       </c>
@@ -6795,7 +7021,7 @@
         <v>5</v>
       </c>
       <c r="G58" s="4">
-        <f>F58/SUMIFS($F:$F,$A:$A,A58,$B:$B,B58)</f>
+        <f t="shared" si="12"/>
         <v>0.05</v>
       </c>
       <c r="H58" s="3" t="b">
@@ -6835,47 +7061,51 @@
         <v>13.333333333333334</v>
       </c>
       <c r="S58">
-        <f t="shared" si="0"/>
-        <v>80</v>
+        <f t="shared" si="1"/>
+        <v>180</v>
       </c>
       <c r="T58">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="V58">
-        <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="W58">
         <f t="shared" si="4"/>
-        <v>33.333333333333336</v>
-      </c>
-      <c r="X58">
+        <v>246.91358024691357</v>
+      </c>
+      <c r="W58" s="11">
         <f t="shared" si="5"/>
+        <v>66.666666666666671</v>
+      </c>
+      <c r="X58" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="Z58">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>80</v>
+      </c>
+      <c r="AA58">
+        <f t="shared" si="9"/>
         <v>45</v>
       </c>
-      <c r="AA58" s="11">
-        <f t="shared" si="8"/>
-        <v>673.33333333333326</v>
-      </c>
       <c r="AB58" s="11">
-        <f t="shared" si="9"/>
-        <v>67.333333333333329</v>
-      </c>
-    </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>978.58024691358025</v>
+      </c>
+      <c r="AC58" s="11">
+        <f t="shared" si="11"/>
+        <v>97.858024691358025</v>
+      </c>
+    </row>
+    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>135</v>
       </c>
@@ -6895,7 +7125,7 @@
         <v>39</v>
       </c>
       <c r="G59" s="4">
-        <f>F59/SUMIFS($F:$F,$A:$A,A59,$B:$B,B59)</f>
+        <f t="shared" si="12"/>
         <v>0.39</v>
       </c>
       <c r="H59" s="3" t="b">
@@ -6915,7 +7145,7 @@
         <v>180</v>
       </c>
       <c r="M59" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N59" s="3">
         <v>8</v>
@@ -6935,47 +7165,51 @@
         <v>4.166666666666667</v>
       </c>
       <c r="S59">
-        <f t="shared" si="0"/>
-        <v>10.256410256410257</v>
+        <f t="shared" si="1"/>
+        <v>44</v>
       </c>
       <c r="T59">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U59">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="V59">
-        <f t="shared" si="3"/>
-        <v>60</v>
-      </c>
-      <c r="W59">
         <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="X59">
+        <v>61.728395061728392</v>
+      </c>
+      <c r="W59" s="11">
         <f t="shared" si="5"/>
+        <v>66.666666666666671</v>
+      </c>
+      <c r="X59" s="11">
+        <f t="shared" si="6"/>
         <v>31.25</v>
       </c>
       <c r="Y59">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z59">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>25</v>
+      </c>
+      <c r="AA59">
+        <f t="shared" si="9"/>
         <v>45</v>
       </c>
-      <c r="AA59" s="11">
-        <f t="shared" si="8"/>
-        <v>336.50641025641028</v>
-      </c>
       <c r="AB59" s="11">
-        <f t="shared" si="9"/>
-        <v>33.650641025641029</v>
-      </c>
-    </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>313.64506172839509</v>
+      </c>
+      <c r="AC59" s="11">
+        <f t="shared" si="11"/>
+        <v>31.364506172839508</v>
+      </c>
+    </row>
+    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>135</v>
       </c>
@@ -6995,7 +7229,7 @@
         <v>1</v>
       </c>
       <c r="G60" s="4">
-        <f>F60/SUMIFS($F:$F,$A:$A,A60,$B:$B,B60)</f>
+        <f t="shared" si="12"/>
         <v>0.01</v>
       </c>
       <c r="H60" s="3" t="b">
@@ -7035,47 +7269,51 @@
         <v>18.333333333333332</v>
       </c>
       <c r="S60">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <f t="shared" si="1"/>
+        <v>196</v>
       </c>
       <c r="T60">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U60">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>120</v>
       </c>
       <c r="V60">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
+        <v>312.49999999999994</v>
+      </c>
+      <c r="W60" s="11">
+        <f t="shared" si="5"/>
+        <v>66.666666666666671</v>
+      </c>
+      <c r="X60" s="11">
+        <f t="shared" si="6"/>
+        <v>80</v>
+      </c>
+      <c r="Y60">
+        <f t="shared" si="7"/>
+        <v>62.5</v>
+      </c>
+      <c r="Z60">
+        <f t="shared" si="8"/>
         <v>110</v>
       </c>
-      <c r="W60">
-        <f t="shared" si="4"/>
-        <v>33.333333333333336</v>
-      </c>
-      <c r="X60">
-        <f t="shared" si="5"/>
-        <v>80</v>
-      </c>
-      <c r="Y60">
-        <f t="shared" si="6"/>
-        <v>62.5</v>
-      </c>
-      <c r="Z60">
-        <f t="shared" si="7"/>
+      <c r="AA60">
+        <f t="shared" si="9"/>
         <v>55</v>
       </c>
-      <c r="AA60" s="11">
-        <f t="shared" si="8"/>
-        <v>1060.8333333333335</v>
-      </c>
       <c r="AB60" s="11">
-        <f t="shared" si="9"/>
-        <v>106.08333333333334</v>
-      </c>
-    </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1152.6666666666665</v>
+      </c>
+      <c r="AC60" s="11">
+        <f t="shared" si="11"/>
+        <v>115.26666666666665</v>
+      </c>
+    </row>
+    <row r="61" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>135</v>
       </c>
@@ -7095,7 +7333,7 @@
         <v>20</v>
       </c>
       <c r="G61" s="4">
-        <f>F61/SUMIFS($F:$F,$A:$A,A61,$B:$B,B61)</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="H61" s="3" t="b">
@@ -7135,47 +7373,51 @@
         <v>6.666666666666667</v>
       </c>
       <c r="S61">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>120</v>
       </c>
       <c r="T61">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="V61">
-        <f t="shared" si="3"/>
-        <v>85</v>
-      </c>
-      <c r="W61">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X61">
+        <v>118.34319526627218</v>
+      </c>
+      <c r="W61" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X61" s="11">
+        <f t="shared" si="6"/>
         <v>35.555555555555557</v>
       </c>
       <c r="Y61">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="Z61">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>40</v>
+      </c>
+      <c r="AA61">
+        <f t="shared" si="9"/>
         <v>60</v>
       </c>
-      <c r="AA61" s="11">
-        <f t="shared" si="8"/>
-        <v>392.22222222222223</v>
-      </c>
       <c r="AB61" s="11">
-        <f t="shared" si="9"/>
-        <v>39.222222222222221</v>
-      </c>
-    </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>582.23208415516103</v>
+      </c>
+      <c r="AC61" s="11">
+        <f t="shared" si="11"/>
+        <v>58.223208415516105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>135</v>
       </c>
@@ -7195,7 +7437,7 @@
         <v>2</v>
       </c>
       <c r="G62" s="4">
-        <f>F62/SUMIFS($F:$F,$A:$A,A62,$B:$B,B62)</f>
+        <f t="shared" si="12"/>
         <v>0.02</v>
       </c>
       <c r="H62" s="3" t="b">
@@ -7235,47 +7477,51 @@
         <v>16.666666666666668</v>
       </c>
       <c r="S62">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <f t="shared" si="1"/>
+        <v>192</v>
       </c>
       <c r="T62">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U62">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="V62">
-        <f t="shared" si="3"/>
-        <v>110</v>
-      </c>
-      <c r="W62">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X62">
+        <v>312.49999999999994</v>
+      </c>
+      <c r="W62" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X62" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y62">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>62.5</v>
       </c>
       <c r="Z62">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+      <c r="AA62">
+        <f t="shared" si="9"/>
         <v>75</v>
       </c>
-      <c r="AA62" s="11">
-        <f t="shared" si="8"/>
-        <v>874.16666666666663</v>
-      </c>
       <c r="AB62" s="11">
-        <f t="shared" si="9"/>
-        <v>87.416666666666657</v>
-      </c>
-    </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1185.3333333333335</v>
+      </c>
+      <c r="AC62" s="11">
+        <f t="shared" si="11"/>
+        <v>118.53333333333335</v>
+      </c>
+    </row>
+    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>135</v>
       </c>
@@ -7295,7 +7541,7 @@
         <v>19</v>
       </c>
       <c r="G63" s="4">
-        <f>F63/SUMIFS($F:$F,$A:$A,A63,$B:$B,B63)</f>
+        <f t="shared" si="12"/>
         <v>0.19</v>
       </c>
       <c r="H63" s="3" t="b">
@@ -7335,47 +7581,51 @@
         <v>20.833333333333332</v>
       </c>
       <c r="S63">
-        <f t="shared" si="0"/>
-        <v>21.05263157894737</v>
+        <f t="shared" si="1"/>
+        <v>124</v>
       </c>
       <c r="T63">
-        <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="U63">
         <f t="shared" si="2"/>
         <v>150</v>
       </c>
+      <c r="U63">
+        <f t="shared" si="3"/>
+        <v>150</v>
+      </c>
       <c r="V63">
-        <f t="shared" si="3"/>
-        <v>75</v>
-      </c>
-      <c r="W63">
         <f t="shared" si="4"/>
-        <v>22.222222222222221</v>
-      </c>
-      <c r="X63">
+        <v>88.888888888888886</v>
+      </c>
+      <c r="W63" s="11">
         <f t="shared" si="5"/>
+        <v>44.444444444444443</v>
+      </c>
+      <c r="X63" s="11">
+        <f t="shared" si="6"/>
         <v>125</v>
       </c>
       <c r="Y63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>125</v>
+      </c>
+      <c r="AA63">
+        <f t="shared" si="9"/>
         <v>25</v>
       </c>
-      <c r="AA63" s="11">
-        <f t="shared" si="8"/>
-        <v>618.27485380116968</v>
-      </c>
       <c r="AB63" s="11">
-        <f t="shared" si="9"/>
-        <v>61.827485380116968</v>
-      </c>
-    </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>832.33333333333337</v>
+      </c>
+      <c r="AC63" s="11">
+        <f t="shared" si="11"/>
+        <v>83.233333333333334</v>
+      </c>
+    </row>
+    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>135</v>
       </c>
@@ -7395,7 +7645,7 @@
         <v>1</v>
       </c>
       <c r="G64" s="4">
-        <f>F64/SUMIFS($F:$F,$A:$A,A64,$B:$B,B64)</f>
+        <f t="shared" si="12"/>
         <v>0.01</v>
       </c>
       <c r="H64" s="3" t="b">
@@ -7435,47 +7685,51 @@
         <v>41.666666666666664</v>
       </c>
       <c r="S64">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <f t="shared" si="1"/>
+        <v>196</v>
       </c>
       <c r="T64">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>250</v>
       </c>
       <c r="V64">
-        <f t="shared" si="3"/>
-        <v>90</v>
-      </c>
-      <c r="W64">
         <f t="shared" si="4"/>
-        <v>25</v>
-      </c>
-      <c r="X64">
+        <v>138.88888888888889</v>
+      </c>
+      <c r="W64" s="11">
         <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="X64" s="11">
+        <f t="shared" si="6"/>
         <v>222.22222222222223</v>
       </c>
       <c r="Y64">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>75</v>
       </c>
       <c r="Z64">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>250</v>
+      </c>
+      <c r="AA64">
+        <f t="shared" si="9"/>
         <v>50</v>
       </c>
-      <c r="AA64" s="11">
-        <f t="shared" si="8"/>
-        <v>1312.2222222222222</v>
-      </c>
       <c r="AB64" s="11">
-        <f t="shared" si="9"/>
-        <v>131.22222222222223</v>
-      </c>
-    </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1382.1111111111111</v>
+      </c>
+      <c r="AC64" s="11">
+        <f t="shared" si="11"/>
+        <v>138.21111111111111</v>
+      </c>
+    </row>
+    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>135</v>
       </c>
@@ -7495,7 +7749,7 @@
         <v>30</v>
       </c>
       <c r="G65" s="4">
-        <f>F65/SUMIFS($F:$F,$A:$A,A65,$B:$B,B65)</f>
+        <f t="shared" si="12"/>
         <v>0.3</v>
       </c>
       <c r="H65" s="3" t="b">
@@ -7535,47 +7789,51 @@
         <v>7.083333333333333</v>
       </c>
       <c r="S65">
-        <f t="shared" si="0"/>
-        <v>13.333333333333334</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
       <c r="T65">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="U65">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="V65">
-        <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="W65">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X65">
+        <v>165.28925619834709</v>
+      </c>
+      <c r="W65" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X65" s="11">
+        <f t="shared" si="6"/>
         <v>40.816326530612244</v>
       </c>
       <c r="Y65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="Z65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>42.5</v>
+      </c>
+      <c r="AA65">
+        <f t="shared" si="9"/>
         <v>65</v>
       </c>
-      <c r="AA65" s="11">
-        <f t="shared" si="8"/>
-        <v>430.81632653061223</v>
-      </c>
       <c r="AB65" s="11">
-        <f t="shared" si="9"/>
-        <v>43.08163265306122</v>
-      </c>
-    </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>626.93891606229272</v>
+      </c>
+      <c r="AC65" s="11">
+        <f t="shared" si="11"/>
+        <v>62.693891606229272</v>
+      </c>
+    </row>
+    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>135</v>
       </c>
@@ -7595,7 +7853,7 @@
         <v>10</v>
       </c>
       <c r="G66" s="4">
-        <f>F66/SUMIFS($F:$F,$A:$A,A66,$B:$B,B66)</f>
+        <f t="shared" ref="G66:G97" si="13">F66/SUMIFS($F:$F,$A:$A,A66,$B:$B,B66)</f>
         <v>0.1</v>
       </c>
       <c r="H66" s="3" t="b">
@@ -7635,47 +7893,51 @@
         <v>12.5</v>
       </c>
       <c r="S66">
-        <f t="shared" si="0"/>
-        <v>40</v>
+        <f t="shared" si="1"/>
+        <v>160</v>
       </c>
       <c r="T66">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="U66">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="V66">
-        <f t="shared" si="3"/>
-        <v>110</v>
-      </c>
-      <c r="W66">
         <f t="shared" si="4"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X66">
+        <v>312.49999999999994</v>
+      </c>
+      <c r="W66" s="11">
         <f t="shared" si="5"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X66" s="11">
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="Y66">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>62.5</v>
       </c>
       <c r="Z66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>75</v>
       </c>
-      <c r="AA66" s="11">
-        <f t="shared" si="8"/>
-        <v>724.16666666666674</v>
+      <c r="AA66">
+        <f t="shared" si="9"/>
+        <v>75</v>
       </c>
       <c r="AB66" s="11">
-        <f t="shared" si="9"/>
-        <v>72.416666666666671</v>
-      </c>
-    </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>1138.3333333333335</v>
+      </c>
+      <c r="AC66" s="11">
+        <f t="shared" si="11"/>
+        <v>113.83333333333334</v>
+      </c>
+    </row>
+    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>135</v>
       </c>
@@ -7695,7 +7957,7 @@
         <v>35</v>
       </c>
       <c r="G67" s="4">
-        <f>F67/SUMIFS($F:$F,$A:$A,A67,$B:$B,B67)</f>
+        <f t="shared" si="13"/>
         <v>0.35</v>
       </c>
       <c r="H67" s="3" t="b">
@@ -7735,47 +7997,51 @@
         <v>5.833333333333333</v>
       </c>
       <c r="S67">
-        <f t="shared" ref="S67:S78" si="10">200/(F67/2)</f>
-        <v>11.428571428571429</v>
+        <f t="shared" ref="S67:S78" si="14">(200-F67*4)</f>
+        <v>60</v>
       </c>
       <c r="T67">
-        <f t="shared" ref="T67:T78" si="11">IF(H67,200,50)</f>
+        <f t="shared" ref="T67:T78" si="15">IF(H67,150,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <f t="shared" ref="U67:U78" si="16">100*I67</f>
         <v>50</v>
       </c>
-      <c r="U67">
-        <f t="shared" ref="U67:U78" si="12">100-(100*((1-I67)/2))*2</f>
+      <c r="V67">
+        <f t="shared" ref="V67:V78" si="17">200/((L67/100)*(L67/100))</f>
+        <v>246.91358024691357</v>
+      </c>
+      <c r="W67" s="11">
+        <f t="shared" ref="W67:W78" si="18">(200/M67)</f>
+        <v>100</v>
+      </c>
+      <c r="X67" s="11">
+        <f t="shared" ref="X67:X78" si="19">(20/(N67*N67)*100)</f>
+        <v>40.816326530612244</v>
+      </c>
+      <c r="Y67">
+        <f t="shared" ref="Y67:Y78" si="20">O67/2</f>
         <v>50</v>
       </c>
-      <c r="V67">
-        <f t="shared" ref="V67:V78" si="13">100+(100-L67)/2</f>
-        <v>105</v>
-      </c>
-      <c r="W67">
-        <f t="shared" ref="W67:W78" si="14">(100/M67)</f>
-        <v>50</v>
-      </c>
-      <c r="X67">
-        <f t="shared" ref="X67:X78" si="15">200/(N67*N67)*10</f>
-        <v>40.816326530612244</v>
-      </c>
-      <c r="Y67">
-        <f t="shared" ref="Y67:Y78" si="16">O67/2</f>
-        <v>50</v>
-      </c>
       <c r="Z67">
-        <f t="shared" ref="Z67:Z78" si="17">P67/2</f>
+        <f t="shared" ref="Z67:Z78" si="21">K67/2</f>
+        <v>35</v>
+      </c>
+      <c r="AA67">
+        <f t="shared" ref="AA67:AA78" si="22">P67/2</f>
         <v>60</v>
       </c>
-      <c r="AA67" s="11">
-        <f t="shared" ref="AA67:AA78" si="18">SUM(S67:Z67)</f>
-        <v>417.24489795918367</v>
-      </c>
       <c r="AB67" s="11">
-        <f t="shared" ref="AB67:AB78" si="19">AA67/10</f>
-        <v>41.724489795918366</v>
-      </c>
-    </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" ref="AB67:AB78" si="23">SUM(S67:AA67)</f>
+        <v>642.7299067775258</v>
+      </c>
+      <c r="AC67" s="11">
+        <f t="shared" ref="AC67:AC78" si="24">AB67/10</f>
+        <v>64.272990677752574</v>
+      </c>
+    </row>
+    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>135</v>
       </c>
@@ -7795,7 +8061,7 @@
         <v>5</v>
       </c>
       <c r="G68" s="4">
-        <f>F68/SUMIFS($F:$F,$A:$A,A68,$B:$B,B68)</f>
+        <f t="shared" si="13"/>
         <v>0.05</v>
       </c>
       <c r="H68" s="3" t="b">
@@ -7835,47 +8101,51 @@
         <v>11.666666666666666</v>
       </c>
       <c r="S68">
-        <f t="shared" si="10"/>
-        <v>80</v>
+        <f t="shared" si="14"/>
+        <v>180</v>
       </c>
       <c r="T68">
-        <f t="shared" si="11"/>
-        <v>200</v>
+        <f t="shared" si="15"/>
+        <v>150</v>
       </c>
       <c r="U68">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>90</v>
       </c>
       <c r="V68">
-        <f t="shared" si="13"/>
-        <v>95</v>
-      </c>
-      <c r="W68">
-        <f t="shared" si="14"/>
-        <v>40</v>
-      </c>
-      <c r="X68">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
+        <v>165.28925619834709</v>
+      </c>
+      <c r="W68" s="11">
+        <f t="shared" si="18"/>
+        <v>80</v>
+      </c>
+      <c r="X68" s="11">
+        <f t="shared" si="19"/>
         <v>125</v>
       </c>
       <c r="Y68">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>50</v>
       </c>
       <c r="Z68">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
+        <v>70</v>
+      </c>
+      <c r="AA68">
+        <f t="shared" si="22"/>
         <v>62.5</v>
       </c>
-      <c r="AA68" s="11">
-        <f t="shared" si="18"/>
-        <v>742.5</v>
-      </c>
       <c r="AB68" s="11">
-        <f t="shared" si="19"/>
-        <v>74.25</v>
-      </c>
-    </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>972.78925619834706</v>
+      </c>
+      <c r="AC68" s="11">
+        <f t="shared" si="24"/>
+        <v>97.278925619834709</v>
+      </c>
+    </row>
+    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>135</v>
       </c>
@@ -7895,7 +8165,7 @@
         <v>40</v>
       </c>
       <c r="G69" s="4">
-        <f>F69/SUMIFS($F:$F,$A:$A,A69,$B:$B,B69)</f>
+        <f t="shared" si="13"/>
         <v>0.4</v>
       </c>
       <c r="H69" s="3" t="b">
@@ -7935,47 +8205,51 @@
         <v>5.833333333333333</v>
       </c>
       <c r="S69">
-        <f t="shared" si="10"/>
-        <v>10</v>
-      </c>
-      <c r="T69">
-        <f t="shared" si="11"/>
-        <v>50</v>
-      </c>
-      <c r="U69">
-        <f t="shared" si="12"/>
-        <v>60</v>
-      </c>
-      <c r="V69">
-        <f t="shared" si="13"/>
-        <v>75</v>
-      </c>
-      <c r="W69">
         <f t="shared" si="14"/>
         <v>40</v>
       </c>
-      <c r="X69">
+      <c r="T69">
         <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <f t="shared" si="16"/>
+        <v>60</v>
+      </c>
+      <c r="V69">
+        <f t="shared" si="17"/>
+        <v>88.888888888888886</v>
+      </c>
+      <c r="W69" s="11">
+        <f t="shared" si="18"/>
+        <v>80</v>
+      </c>
+      <c r="X69" s="11">
+        <f t="shared" si="19"/>
         <v>31.25</v>
       </c>
       <c r="Y69">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Z69">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>35</v>
       </c>
-      <c r="AA69" s="11">
-        <f t="shared" si="18"/>
-        <v>301.25</v>
+      <c r="AA69">
+        <f t="shared" si="22"/>
+        <v>35</v>
       </c>
       <c r="AB69" s="11">
-        <f t="shared" si="19"/>
-        <v>30.125</v>
-      </c>
-    </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>370.13888888888891</v>
+      </c>
+      <c r="AC69" s="11">
+        <f t="shared" si="24"/>
+        <v>37.013888888888893</v>
+      </c>
+    </row>
+    <row r="70" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>135</v>
       </c>
@@ -7995,7 +8269,7 @@
         <v>8</v>
       </c>
       <c r="G70" s="4">
-        <f>F70/SUMIFS($F:$F,$A:$A,A70,$B:$B,B70)</f>
+        <f t="shared" si="13"/>
         <v>0.08</v>
       </c>
       <c r="H70" s="3" t="b">
@@ -8035,47 +8309,51 @@
         <v>11.666666666666666</v>
       </c>
       <c r="S70">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
+        <v>168</v>
+      </c>
+      <c r="T70">
+        <f t="shared" si="15"/>
+        <v>150</v>
+      </c>
+      <c r="U70">
+        <f t="shared" si="16"/>
+        <v>150</v>
+      </c>
+      <c r="V70">
+        <f t="shared" si="17"/>
+        <v>165.28925619834709</v>
+      </c>
+      <c r="W70" s="11">
+        <f t="shared" si="18"/>
+        <v>80</v>
+      </c>
+      <c r="X70" s="11">
+        <f t="shared" si="19"/>
+        <v>55.555555555555557</v>
+      </c>
+      <c r="Y70">
+        <f t="shared" si="20"/>
+        <v>37.5</v>
+      </c>
+      <c r="Z70">
+        <f t="shared" si="21"/>
+        <v>70</v>
+      </c>
+      <c r="AA70">
+        <f t="shared" si="22"/>
         <v>50</v>
       </c>
-      <c r="T70">
-        <f t="shared" si="11"/>
-        <v>200</v>
-      </c>
-      <c r="U70">
-        <f t="shared" si="12"/>
-        <v>150</v>
-      </c>
-      <c r="V70">
-        <f t="shared" si="13"/>
-        <v>95</v>
-      </c>
-      <c r="W70">
-        <f t="shared" si="14"/>
-        <v>40</v>
-      </c>
-      <c r="X70">
-        <f t="shared" si="15"/>
-        <v>55.555555555555557</v>
-      </c>
-      <c r="Y70">
-        <f t="shared" si="16"/>
-        <v>37.5</v>
-      </c>
-      <c r="Z70">
-        <f t="shared" si="17"/>
-        <v>50</v>
-      </c>
-      <c r="AA70" s="11">
-        <f t="shared" si="18"/>
-        <v>678.05555555555554</v>
-      </c>
       <c r="AB70" s="11">
-        <f t="shared" si="19"/>
-        <v>67.805555555555557</v>
-      </c>
-    </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>926.3448117539026</v>
+      </c>
+      <c r="AC70" s="11">
+        <f t="shared" si="24"/>
+        <v>92.634481175390263</v>
+      </c>
+    </row>
+    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>135</v>
       </c>
@@ -8095,7 +8373,7 @@
         <v>8</v>
       </c>
       <c r="G71" s="4">
-        <f>F71/SUMIFS($F:$F,$A:$A,A71,$B:$B,B71)</f>
+        <f t="shared" si="13"/>
         <v>0.08</v>
       </c>
       <c r="H71" s="3" t="b">
@@ -8109,7 +8387,7 @@
         <v>2.8111111111111104</v>
       </c>
       <c r="K71" s="3">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="L71" s="3">
         <v>75</v>
@@ -8124,58 +8402,62 @@
         <v>100</v>
       </c>
       <c r="P71" s="3">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="Q71" s="6">
         <f>K71/Notes!$B$5</f>
-        <v>37.5</v>
+        <v>45</v>
       </c>
       <c r="R71" s="6">
         <f>K71/(Notes!$B$5+Notes!$B$6)</f>
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="S71">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
+        <v>168</v>
+      </c>
+      <c r="T71">
+        <f t="shared" si="15"/>
+        <v>150</v>
+      </c>
+      <c r="U71">
+        <f t="shared" si="16"/>
+        <v>110.00000000000001</v>
+      </c>
+      <c r="V71">
+        <f t="shared" si="17"/>
+        <v>355.55555555555554</v>
+      </c>
+      <c r="W71" s="11">
+        <f t="shared" si="18"/>
+        <v>100</v>
+      </c>
+      <c r="X71" s="11">
+        <f t="shared" si="19"/>
+        <v>55.555555555555557</v>
+      </c>
+      <c r="Y71">
+        <f t="shared" si="20"/>
         <v>50</v>
       </c>
-      <c r="T71">
-        <f t="shared" si="11"/>
-        <v>200</v>
-      </c>
-      <c r="U71">
-        <f t="shared" si="12"/>
-        <v>110.00000000000001</v>
-      </c>
-      <c r="V71">
-        <f t="shared" si="13"/>
-        <v>112.5</v>
-      </c>
-      <c r="W71">
-        <f t="shared" si="14"/>
-        <v>50</v>
-      </c>
-      <c r="X71">
-        <f t="shared" si="15"/>
-        <v>55.555555555555557</v>
-      </c>
-      <c r="Y71">
-        <f t="shared" si="16"/>
-        <v>50</v>
-      </c>
       <c r="Z71">
-        <f t="shared" si="17"/>
-        <v>90</v>
-      </c>
-      <c r="AA71" s="11">
-        <f t="shared" si="18"/>
-        <v>718.05555555555554</v>
+        <f t="shared" si="21"/>
+        <v>45</v>
+      </c>
+      <c r="AA71">
+        <f t="shared" si="22"/>
+        <v>80</v>
       </c>
       <c r="AB71" s="11">
-        <f t="shared" si="19"/>
-        <v>71.805555555555557</v>
-      </c>
-    </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>1114.1111111111111</v>
+      </c>
+      <c r="AC71" s="11">
+        <f t="shared" si="24"/>
+        <v>111.41111111111111</v>
+      </c>
+    </row>
+    <row r="72" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>135</v>
       </c>
@@ -8195,7 +8477,7 @@
         <v>10</v>
       </c>
       <c r="G72" s="4">
-        <f>F72/SUMIFS($F:$F,$A:$A,A72,$B:$B,B72)</f>
+        <f t="shared" si="13"/>
         <v>0.1</v>
       </c>
       <c r="H72" s="3" t="b">
@@ -8235,47 +8517,51 @@
         <v>15.833333333333334</v>
       </c>
       <c r="S72">
-        <f t="shared" si="10"/>
-        <v>40</v>
+        <f t="shared" si="14"/>
+        <v>160</v>
       </c>
       <c r="T72">
-        <f t="shared" si="11"/>
-        <v>200</v>
+        <f t="shared" si="15"/>
+        <v>150</v>
       </c>
       <c r="U72">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>100</v>
       </c>
       <c r="V72">
-        <f t="shared" si="13"/>
-        <v>107.5</v>
-      </c>
-      <c r="W72">
-        <f t="shared" si="14"/>
-        <v>50</v>
-      </c>
-      <c r="X72">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
+        <v>276.8166089965398</v>
+      </c>
+      <c r="W72" s="11">
+        <f t="shared" si="18"/>
+        <v>100</v>
+      </c>
+      <c r="X72" s="11">
+        <f t="shared" si="19"/>
         <v>80</v>
       </c>
       <c r="Y72">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>62.5</v>
       </c>
       <c r="Z72">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
+        <v>95</v>
+      </c>
+      <c r="AA72">
+        <f t="shared" si="22"/>
         <v>65</v>
       </c>
-      <c r="AA72" s="11">
-        <f t="shared" si="18"/>
-        <v>705</v>
-      </c>
       <c r="AB72" s="11">
-        <f t="shared" si="19"/>
-        <v>70.5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>1089.3166089965398</v>
+      </c>
+      <c r="AC72" s="11">
+        <f t="shared" si="24"/>
+        <v>108.93166089965398</v>
+      </c>
+    </row>
+    <row r="73" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>135</v>
       </c>
@@ -8295,7 +8581,7 @@
         <v>34</v>
       </c>
       <c r="G73" s="4">
-        <f>F73/SUMIFS($F:$F,$A:$A,A73,$B:$B,B73)</f>
+        <f t="shared" si="13"/>
         <v>0.34</v>
       </c>
       <c r="H73" s="3" t="b">
@@ -8335,47 +8621,51 @@
         <v>16.666666666666668</v>
       </c>
       <c r="S73">
-        <f t="shared" si="10"/>
-        <v>11.764705882352942</v>
+        <f t="shared" si="14"/>
+        <v>64</v>
       </c>
       <c r="T73">
-        <f t="shared" si="11"/>
-        <v>50</v>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="U73">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>120</v>
       </c>
       <c r="V73">
-        <f t="shared" si="13"/>
-        <v>75</v>
-      </c>
-      <c r="W73">
-        <f t="shared" si="14"/>
-        <v>28.571428571428573</v>
-      </c>
-      <c r="X73">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
+        <v>88.888888888888886</v>
+      </c>
+      <c r="W73" s="11">
+        <f t="shared" si="18"/>
+        <v>57.142857142857146</v>
+      </c>
+      <c r="X73" s="11">
+        <f t="shared" si="19"/>
         <v>80</v>
       </c>
       <c r="Y73">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="Z73">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
+        <v>100</v>
+      </c>
+      <c r="AA73">
+        <f t="shared" si="22"/>
         <v>25</v>
       </c>
-      <c r="AA73" s="11">
-        <f t="shared" si="18"/>
-        <v>420.33613445378148</v>
-      </c>
       <c r="AB73" s="11">
-        <f t="shared" si="19"/>
-        <v>42.033613445378151</v>
-      </c>
-    </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>565.03174603174602</v>
+      </c>
+      <c r="AC73" s="11">
+        <f t="shared" si="24"/>
+        <v>56.5031746031746</v>
+      </c>
+    </row>
+    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>135</v>
       </c>
@@ -8395,7 +8685,7 @@
         <v>33</v>
       </c>
       <c r="G74" s="4">
-        <f>F74/SUMIFS($F:$F,$A:$A,A74,$B:$B,B74)</f>
+        <f t="shared" si="13"/>
         <v>0.33</v>
       </c>
       <c r="H74" s="3" t="b">
@@ -8435,47 +8725,51 @@
         <v>7.083333333333333</v>
       </c>
       <c r="S74">
-        <f t="shared" si="10"/>
-        <v>12.121212121212121</v>
+        <f t="shared" si="14"/>
+        <v>68</v>
       </c>
       <c r="T74">
-        <f t="shared" si="11"/>
-        <v>50</v>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="U74">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>70</v>
       </c>
       <c r="V74">
-        <f t="shared" si="13"/>
-        <v>90</v>
-      </c>
-      <c r="W74">
-        <f t="shared" si="14"/>
-        <v>50</v>
-      </c>
-      <c r="X74">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
+        <v>138.88888888888889</v>
+      </c>
+      <c r="W74" s="11">
+        <f t="shared" si="18"/>
+        <v>100</v>
+      </c>
+      <c r="X74" s="11">
+        <f t="shared" si="19"/>
         <v>40.816326530612244</v>
       </c>
       <c r="Y74">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>5</v>
       </c>
       <c r="Z74">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
+        <v>42.5</v>
+      </c>
+      <c r="AA74">
+        <f t="shared" si="22"/>
         <v>40</v>
       </c>
-      <c r="AA74" s="11">
-        <f t="shared" si="18"/>
-        <v>357.93753865182435</v>
-      </c>
       <c r="AB74" s="11">
-        <f t="shared" si="19"/>
-        <v>35.793753865182438</v>
-      </c>
-    </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>505.20521541950114</v>
+      </c>
+      <c r="AC74" s="11">
+        <f t="shared" si="24"/>
+        <v>50.520521541950117</v>
+      </c>
+    </row>
+    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>135</v>
       </c>
@@ -8495,7 +8789,7 @@
         <v>8</v>
       </c>
       <c r="G75" s="4">
-        <f>F75/SUMIFS($F:$F,$A:$A,A75,$B:$B,B75)</f>
+        <f t="shared" si="13"/>
         <v>0.08</v>
       </c>
       <c r="H75" s="3" t="b">
@@ -8535,47 +8829,51 @@
         <v>12.5</v>
       </c>
       <c r="S75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
+        <v>168</v>
+      </c>
+      <c r="T75">
+        <f t="shared" si="15"/>
+        <v>150</v>
+      </c>
+      <c r="U75">
+        <f t="shared" si="16"/>
+        <v>70</v>
+      </c>
+      <c r="V75">
+        <f t="shared" si="17"/>
+        <v>276.8166089965398</v>
+      </c>
+      <c r="W75" s="11">
+        <f t="shared" si="18"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X75" s="11">
+        <f t="shared" si="19"/>
+        <v>80</v>
+      </c>
+      <c r="Y75">
+        <f t="shared" si="20"/>
         <v>50</v>
       </c>
-      <c r="T75">
-        <f t="shared" si="11"/>
-        <v>200</v>
-      </c>
-      <c r="U75">
-        <f t="shared" si="12"/>
-        <v>70</v>
-      </c>
-      <c r="V75">
-        <f t="shared" si="13"/>
-        <v>107.5</v>
-      </c>
-      <c r="W75">
-        <f t="shared" si="14"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X75">
-        <f t="shared" si="15"/>
-        <v>80</v>
-      </c>
-      <c r="Y75">
-        <f t="shared" si="16"/>
-        <v>50</v>
-      </c>
       <c r="Z75">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
+        <v>75</v>
+      </c>
+      <c r="AA75">
+        <f t="shared" si="22"/>
         <v>60</v>
       </c>
-      <c r="AA75" s="11">
-        <f t="shared" si="18"/>
-        <v>684.16666666666674</v>
-      </c>
       <c r="AB75" s="11">
-        <f t="shared" si="19"/>
-        <v>68.416666666666671</v>
-      </c>
-    </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>1063.1499423298733</v>
+      </c>
+      <c r="AC75" s="11">
+        <f t="shared" si="24"/>
+        <v>106.31499423298733</v>
+      </c>
+    </row>
+    <row r="76" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>135</v>
       </c>
@@ -8595,7 +8893,7 @@
         <v>39</v>
       </c>
       <c r="G76" s="4">
-        <f>F76/SUMIFS($F:$F,$A:$A,A76,$B:$B,B76)</f>
+        <f t="shared" si="13"/>
         <v>0.39</v>
       </c>
       <c r="H76" s="3" t="b">
@@ -8635,47 +8933,51 @@
         <v>6.666666666666667</v>
       </c>
       <c r="S76">
-        <f t="shared" si="10"/>
-        <v>10.256410256410257</v>
+        <f t="shared" si="14"/>
+        <v>44</v>
       </c>
       <c r="T76">
-        <f t="shared" si="11"/>
-        <v>50</v>
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="U76">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>70</v>
       </c>
       <c r="V76">
-        <f t="shared" si="13"/>
-        <v>105</v>
-      </c>
-      <c r="W76">
-        <f t="shared" si="14"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X76">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
+        <v>246.91358024691357</v>
+      </c>
+      <c r="W76" s="11">
+        <f t="shared" si="18"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X76" s="11">
+        <f t="shared" si="19"/>
         <v>40.816326530612244</v>
       </c>
       <c r="Y76">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="Z76">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="AA76">
+        <f t="shared" si="22"/>
         <v>60</v>
       </c>
-      <c r="AA76" s="11">
-        <f t="shared" si="18"/>
-        <v>432.73940345368914</v>
-      </c>
       <c r="AB76" s="11">
-        <f t="shared" si="19"/>
-        <v>43.273940345368914</v>
-      </c>
-    </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>665.06324011085917</v>
+      </c>
+      <c r="AC76" s="11">
+        <f t="shared" si="24"/>
+        <v>66.506324011085923</v>
+      </c>
+    </row>
+    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>135</v>
       </c>
@@ -8695,7 +8997,7 @@
         <v>8</v>
       </c>
       <c r="G77" s="4">
-        <f>F77/SUMIFS($F:$F,$A:$A,A77,$B:$B,B77)</f>
+        <f t="shared" si="13"/>
         <v>0.08</v>
       </c>
       <c r="H77" s="3" t="b">
@@ -8735,47 +9037,51 @@
         <v>14.166666666666666</v>
       </c>
       <c r="S77">
-        <f t="shared" si="10"/>
-        <v>50</v>
+        <f t="shared" si="14"/>
+        <v>168</v>
       </c>
       <c r="T77">
-        <f t="shared" si="11"/>
-        <v>200</v>
+        <f t="shared" si="15"/>
+        <v>150</v>
       </c>
       <c r="U77">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>100</v>
       </c>
       <c r="V77">
-        <f t="shared" si="13"/>
-        <v>112.5</v>
-      </c>
-      <c r="W77">
-        <f t="shared" si="14"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="X77">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
+        <v>355.55555555555554</v>
+      </c>
+      <c r="W77" s="11">
+        <f t="shared" si="18"/>
+        <v>133.33333333333334</v>
+      </c>
+      <c r="X77" s="11">
+        <f t="shared" si="19"/>
         <v>80</v>
       </c>
       <c r="Y77">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>62.5</v>
       </c>
       <c r="Z77">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
+        <v>85</v>
+      </c>
+      <c r="AA77">
+        <f t="shared" si="22"/>
         <v>75</v>
       </c>
-      <c r="AA77" s="11">
-        <f t="shared" si="18"/>
-        <v>746.66666666666663</v>
-      </c>
       <c r="AB77" s="11">
-        <f t="shared" si="19"/>
-        <v>74.666666666666657</v>
-      </c>
-    </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>1209.3888888888889</v>
+      </c>
+      <c r="AC77" s="11">
+        <f t="shared" si="24"/>
+        <v>120.9388888888889</v>
+      </c>
+    </row>
+    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>135</v>
       </c>
@@ -8795,7 +9101,7 @@
         <v>12</v>
       </c>
       <c r="G78" s="4">
-        <f>F78/SUMIFS($F:$F,$A:$A,A78,$B:$B,B78)</f>
+        <f t="shared" si="13"/>
         <v>0.12</v>
       </c>
       <c r="H78" s="3" t="b">
@@ -8835,49 +9141,53 @@
         <v>18.333333333333332</v>
       </c>
       <c r="S78">
-        <f t="shared" si="10"/>
-        <v>33.333333333333336</v>
+        <f t="shared" si="14"/>
+        <v>152</v>
       </c>
       <c r="T78">
-        <f t="shared" si="11"/>
-        <v>200</v>
+        <f t="shared" si="15"/>
+        <v>150</v>
       </c>
       <c r="U78">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>100</v>
       </c>
       <c r="V78">
-        <f t="shared" si="13"/>
-        <v>107.5</v>
-      </c>
-      <c r="W78">
-        <f t="shared" si="14"/>
-        <v>33.333333333333336</v>
-      </c>
-      <c r="X78">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
+        <v>276.8166089965398</v>
+      </c>
+      <c r="W78" s="11">
+        <f t="shared" si="18"/>
+        <v>66.666666666666671</v>
+      </c>
+      <c r="X78" s="11">
+        <f t="shared" si="19"/>
         <v>125</v>
       </c>
       <c r="Y78">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>55</v>
       </c>
       <c r="Z78">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
+        <v>110</v>
+      </c>
+      <c r="AA78">
+        <f t="shared" si="22"/>
         <v>30</v>
       </c>
-      <c r="AA78" s="11">
-        <f t="shared" si="18"/>
-        <v>684.16666666666674</v>
-      </c>
       <c r="AB78" s="11">
-        <f t="shared" si="19"/>
-        <v>68.416666666666671</v>
+        <f t="shared" si="23"/>
+        <v>1065.4832756632063</v>
+      </c>
+      <c r="AC78" s="11">
+        <f t="shared" si="24"/>
+        <v>106.54832756632064</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:R78" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="AA1:AA1048576">
+  <conditionalFormatting sqref="AB1:AB1048576">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -8889,7 +9199,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB1:AB1048576">
+  <conditionalFormatting sqref="AC1:AC1048576">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
